--- a/assets/inputs.xlsx
+++ b/assets/inputs.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crisp\Desktop\infrastructureinmotion\model_app\base_app\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A67AC07-F287-45EF-A0B4-054CF2FC4E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688B7737-BB47-4588-8B47-AC8FE380A852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="supression" sheetId="1" r:id="rId1"/>
     <sheet name="measured_speed" sheetId="2" r:id="rId2"/>
     <sheet name="growth_LV" sheetId="3" r:id="rId3"/>
     <sheet name="growth_HV" sheetId="4" r:id="rId4"/>
+    <sheet name="counts" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="53">
   <si>
     <t>Night</t>
   </si>
@@ -154,6 +155,39 @@
   </si>
   <si>
     <t>S10</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>AADT</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t>Lights</t>
+  </si>
+  <si>
+    <t>Medium A</t>
+  </si>
+  <si>
+    <t>Medium B</t>
+  </si>
+  <si>
+    <t>Heavy A</t>
+  </si>
+  <si>
+    <t>Heavy B</t>
+  </si>
+  <si>
+    <t>NB</t>
   </si>
 </sst>
 </file>
@@ -5894,4 +5928,9560 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B7B1FB9-CC92-45D7-AE69-735DFEAA64D2}">
+  <dimension ref="A1:AB111"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1">
+        <v>0</v>
+      </c>
+      <c r="F1">
+        <v>1</v>
+      </c>
+      <c r="G1">
+        <v>2</v>
+      </c>
+      <c r="H1">
+        <v>3</v>
+      </c>
+      <c r="I1">
+        <v>4</v>
+      </c>
+      <c r="J1">
+        <v>5</v>
+      </c>
+      <c r="K1">
+        <v>6</v>
+      </c>
+      <c r="L1">
+        <v>7</v>
+      </c>
+      <c r="M1">
+        <v>8</v>
+      </c>
+      <c r="N1">
+        <v>9</v>
+      </c>
+      <c r="O1">
+        <v>10</v>
+      </c>
+      <c r="P1">
+        <v>11</v>
+      </c>
+      <c r="Q1">
+        <v>12</v>
+      </c>
+      <c r="R1">
+        <v>13</v>
+      </c>
+      <c r="S1">
+        <v>14</v>
+      </c>
+      <c r="T1">
+        <v>15</v>
+      </c>
+      <c r="U1">
+        <v>16</v>
+      </c>
+      <c r="V1">
+        <v>17</v>
+      </c>
+      <c r="W1">
+        <v>18</v>
+      </c>
+      <c r="X1">
+        <v>19</v>
+      </c>
+      <c r="Y1">
+        <v>20</v>
+      </c>
+      <c r="Z1">
+        <v>21</v>
+      </c>
+      <c r="AA1">
+        <v>22</v>
+      </c>
+      <c r="AB1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2">
+        <v>77419.588610000006</v>
+      </c>
+      <c r="E2">
+        <v>1173.434483</v>
+      </c>
+      <c r="F2">
+        <v>1031.824924</v>
+      </c>
+      <c r="G2">
+        <v>810.20689660000005</v>
+      </c>
+      <c r="H2">
+        <v>892.13793099999998</v>
+      </c>
+      <c r="I2">
+        <v>1231.6965520000001</v>
+      </c>
+      <c r="J2">
+        <v>2216.6896550000001</v>
+      </c>
+      <c r="K2">
+        <v>3075.144828</v>
+      </c>
+      <c r="L2">
+        <v>2310.4551719999999</v>
+      </c>
+      <c r="M2">
+        <v>3043.8626859999999</v>
+      </c>
+      <c r="N2">
+        <v>2143.4709149999999</v>
+      </c>
+      <c r="O2">
+        <v>2505.594188</v>
+      </c>
+      <c r="P2">
+        <v>4141.0574710000001</v>
+      </c>
+      <c r="Q2">
+        <v>4194.6666670000004</v>
+      </c>
+      <c r="R2">
+        <v>4391.9080459999996</v>
+      </c>
+      <c r="S2">
+        <v>4488</v>
+      </c>
+      <c r="T2">
+        <v>3829.517241</v>
+      </c>
+      <c r="U2">
+        <v>5018.6298850000003</v>
+      </c>
+      <c r="V2">
+        <v>5144.662069</v>
+      </c>
+      <c r="W2">
+        <v>6271.8712640000003</v>
+      </c>
+      <c r="X2">
+        <v>6448.5922220000002</v>
+      </c>
+      <c r="Y2">
+        <v>4123.8620689999998</v>
+      </c>
+      <c r="Z2">
+        <v>3527.5862069999998</v>
+      </c>
+      <c r="AA2">
+        <v>3152.5241380000002</v>
+      </c>
+      <c r="AB2">
+        <v>2252.1931030000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3">
+        <v>1592.430036</v>
+      </c>
+      <c r="E3">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="F3">
+        <v>20.69767388</v>
+      </c>
+      <c r="G3">
+        <v>21</v>
+      </c>
+      <c r="H3">
+        <v>22.5</v>
+      </c>
+      <c r="I3">
+        <v>34.424999999999997</v>
+      </c>
+      <c r="J3">
+        <v>66.825000000000003</v>
+      </c>
+      <c r="K3">
+        <v>89.1</v>
+      </c>
+      <c r="L3">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="M3">
+        <v>96.390042829999999</v>
+      </c>
+      <c r="N3">
+        <v>89.633780029999997</v>
+      </c>
+      <c r="O3">
+        <v>75.013774350000006</v>
+      </c>
+      <c r="P3">
+        <v>110.25</v>
+      </c>
+      <c r="Q3">
+        <v>144</v>
+      </c>
+      <c r="R3">
+        <v>111.75</v>
+      </c>
+      <c r="S3">
+        <v>96</v>
+      </c>
+      <c r="T3">
+        <v>57</v>
+      </c>
+      <c r="U3">
+        <v>82.95</v>
+      </c>
+      <c r="V3">
+        <v>92.4</v>
+      </c>
+      <c r="W3">
+        <v>105</v>
+      </c>
+      <c r="X3">
+        <v>85.644765230000004</v>
+      </c>
+      <c r="Y3">
+        <v>44.25</v>
+      </c>
+      <c r="Z3">
+        <v>16.875</v>
+      </c>
+      <c r="AA3">
+        <v>26.324999999999999</v>
+      </c>
+      <c r="AB3">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4">
+        <v>652.81260440000005</v>
+      </c>
+      <c r="E4">
+        <v>13.5</v>
+      </c>
+      <c r="F4">
+        <v>3.942414072</v>
+      </c>
+      <c r="G4">
+        <v>17</v>
+      </c>
+      <c r="H4">
+        <v>23</v>
+      </c>
+      <c r="I4">
+        <v>10.8</v>
+      </c>
+      <c r="J4">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="K4">
+        <v>53.1</v>
+      </c>
+      <c r="L4">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="M4">
+        <v>40.936018189999999</v>
+      </c>
+      <c r="N4">
+        <v>35.512050000000002</v>
+      </c>
+      <c r="O4">
+        <v>39.340557230000002</v>
+      </c>
+      <c r="P4">
+        <v>70</v>
+      </c>
+      <c r="Q4">
+        <v>52</v>
+      </c>
+      <c r="R4">
+        <v>38</v>
+      </c>
+      <c r="S4">
+        <v>37</v>
+      </c>
+      <c r="T4">
+        <v>20</v>
+      </c>
+      <c r="U4">
+        <v>15.4</v>
+      </c>
+      <c r="V4">
+        <v>22.4</v>
+      </c>
+      <c r="W4">
+        <v>26.6</v>
+      </c>
+      <c r="X4">
+        <v>22.281564929999998</v>
+      </c>
+      <c r="Y4">
+        <v>10</v>
+      </c>
+      <c r="Z4">
+        <v>9.9</v>
+      </c>
+      <c r="AA4">
+        <v>7.2</v>
+      </c>
+      <c r="AB4">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5">
+        <v>7898.478701</v>
+      </c>
+      <c r="E5">
+        <v>234</v>
+      </c>
+      <c r="F5">
+        <v>227.67441260000001</v>
+      </c>
+      <c r="G5">
+        <v>253</v>
+      </c>
+      <c r="H5">
+        <v>233</v>
+      </c>
+      <c r="I5">
+        <v>285.3</v>
+      </c>
+      <c r="J5">
+        <v>300.60000000000002</v>
+      </c>
+      <c r="K5">
+        <v>268.2</v>
+      </c>
+      <c r="L5">
+        <v>178.2</v>
+      </c>
+      <c r="M5">
+        <v>327.48814549999997</v>
+      </c>
+      <c r="N5">
+        <v>282.73055190000002</v>
+      </c>
+      <c r="O5">
+        <v>354.7318042</v>
+      </c>
+      <c r="P5">
+        <v>480</v>
+      </c>
+      <c r="Q5">
+        <v>463</v>
+      </c>
+      <c r="R5">
+        <v>455</v>
+      </c>
+      <c r="S5">
+        <v>388</v>
+      </c>
+      <c r="T5">
+        <v>323</v>
+      </c>
+      <c r="U5">
+        <v>387.8</v>
+      </c>
+      <c r="V5">
+        <v>408.8</v>
+      </c>
+      <c r="W5">
+        <v>460.6</v>
+      </c>
+      <c r="X5">
+        <v>516.65378680000003</v>
+      </c>
+      <c r="Y5">
+        <v>339</v>
+      </c>
+      <c r="Z5">
+        <v>267.3</v>
+      </c>
+      <c r="AA5">
+        <v>244.8</v>
+      </c>
+      <c r="AB5">
+        <v>219.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6">
+        <v>440.35763020000002</v>
+      </c>
+      <c r="E6">
+        <v>30.6</v>
+      </c>
+      <c r="F6">
+        <v>35.481726649999999</v>
+      </c>
+      <c r="G6">
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>28</v>
+      </c>
+      <c r="I6">
+        <v>26.1</v>
+      </c>
+      <c r="J6">
+        <v>28.8</v>
+      </c>
+      <c r="K6">
+        <v>14.4</v>
+      </c>
+      <c r="L6">
+        <v>7.8</v>
+      </c>
+      <c r="M6">
+        <v>8.5680038080000003</v>
+      </c>
+      <c r="N6">
+        <v>15.02432885</v>
+      </c>
+      <c r="O6">
+        <v>10.668625690000001</v>
+      </c>
+      <c r="P6">
+        <v>15</v>
+      </c>
+      <c r="Q6">
+        <v>11</v>
+      </c>
+      <c r="R6">
+        <v>13</v>
+      </c>
+      <c r="S6">
+        <v>9</v>
+      </c>
+      <c r="T6">
+        <v>4</v>
+      </c>
+      <c r="U6">
+        <v>5.6</v>
+      </c>
+      <c r="V6">
+        <v>2.8</v>
+      </c>
+      <c r="W6">
+        <v>22.4</v>
+      </c>
+      <c r="X6">
+        <v>34.814945199999997</v>
+      </c>
+      <c r="Y6">
+        <v>23</v>
+      </c>
+      <c r="Z6">
+        <v>24.3</v>
+      </c>
+      <c r="AA6">
+        <v>22.5</v>
+      </c>
+      <c r="AB6">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7">
+        <v>86088.230339999995</v>
+      </c>
+      <c r="E7">
+        <v>906.29885060000004</v>
+      </c>
+      <c r="F7">
+        <v>601.83908050000002</v>
+      </c>
+      <c r="G7">
+        <v>474.39080460000002</v>
+      </c>
+      <c r="H7">
+        <v>708.04597699999999</v>
+      </c>
+      <c r="I7">
+        <v>1467.475862</v>
+      </c>
+      <c r="J7">
+        <v>4256.772414</v>
+      </c>
+      <c r="K7">
+        <v>5339.1724139999997</v>
+      </c>
+      <c r="L7">
+        <v>6163.0901110000004</v>
+      </c>
+      <c r="M7">
+        <v>5178.6482759999999</v>
+      </c>
+      <c r="N7">
+        <v>5282.0229890000001</v>
+      </c>
+      <c r="O7">
+        <v>5182.8965520000002</v>
+      </c>
+      <c r="P7">
+        <v>3826.482759</v>
+      </c>
+      <c r="Q7">
+        <v>3705.1034479999998</v>
+      </c>
+      <c r="R7">
+        <v>3598.8965520000002</v>
+      </c>
+      <c r="S7">
+        <v>3939.7701149999998</v>
+      </c>
+      <c r="T7">
+        <v>3812.3218390000002</v>
+      </c>
+      <c r="U7">
+        <v>4775.0620689999996</v>
+      </c>
+      <c r="V7">
+        <v>5662.9517239999996</v>
+      </c>
+      <c r="W7">
+        <v>5994.3172409999997</v>
+      </c>
+      <c r="X7">
+        <v>5461.8666670000002</v>
+      </c>
+      <c r="Y7">
+        <v>3296.4597699999999</v>
+      </c>
+      <c r="Z7">
+        <v>2865.7655169999998</v>
+      </c>
+      <c r="AA7">
+        <v>2113.82069</v>
+      </c>
+      <c r="AB7">
+        <v>1474.7586209999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8">
+        <v>1891.5511300000001</v>
+      </c>
+      <c r="E8">
+        <v>14.25</v>
+      </c>
+      <c r="F8">
+        <v>27</v>
+      </c>
+      <c r="G8">
+        <v>29.25</v>
+      </c>
+      <c r="H8">
+        <v>29.25</v>
+      </c>
+      <c r="I8">
+        <v>29.7</v>
+      </c>
+      <c r="J8">
+        <v>47.25</v>
+      </c>
+      <c r="K8">
+        <v>113.4</v>
+      </c>
+      <c r="L8">
+        <v>117.05113</v>
+      </c>
+      <c r="M8">
+        <v>156.44999999999999</v>
+      </c>
+      <c r="N8">
+        <v>207.9</v>
+      </c>
+      <c r="O8">
+        <v>170.1</v>
+      </c>
+      <c r="P8">
+        <v>112.5</v>
+      </c>
+      <c r="Q8">
+        <v>108</v>
+      </c>
+      <c r="R8">
+        <v>93</v>
+      </c>
+      <c r="S8">
+        <v>114</v>
+      </c>
+      <c r="T8">
+        <v>66</v>
+      </c>
+      <c r="U8">
+        <v>87.15</v>
+      </c>
+      <c r="V8">
+        <v>68.25</v>
+      </c>
+      <c r="W8">
+        <v>91.35</v>
+      </c>
+      <c r="X8">
+        <v>76.650000000000006</v>
+      </c>
+      <c r="Y8">
+        <v>41.25</v>
+      </c>
+      <c r="Z8">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="AA8">
+        <v>36.450000000000003</v>
+      </c>
+      <c r="AB8">
+        <v>17.55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9">
+        <v>676.32838749999996</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9">
+        <v>9.9</v>
+      </c>
+      <c r="J9">
+        <v>41.4</v>
+      </c>
+      <c r="K9">
+        <v>79.2</v>
+      </c>
+      <c r="L9">
+        <v>53.728387529999999</v>
+      </c>
+      <c r="M9">
+        <v>47.6</v>
+      </c>
+      <c r="N9">
+        <v>57.4</v>
+      </c>
+      <c r="O9">
+        <v>63</v>
+      </c>
+      <c r="P9">
+        <v>41</v>
+      </c>
+      <c r="Q9">
+        <v>45</v>
+      </c>
+      <c r="R9">
+        <v>32</v>
+      </c>
+      <c r="S9">
+        <v>37</v>
+      </c>
+      <c r="T9">
+        <v>26</v>
+      </c>
+      <c r="U9">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="V9">
+        <v>22.4</v>
+      </c>
+      <c r="W9">
+        <v>25.2</v>
+      </c>
+      <c r="X9">
+        <v>21</v>
+      </c>
+      <c r="Y9">
+        <v>7</v>
+      </c>
+      <c r="Z9">
+        <v>5.4</v>
+      </c>
+      <c r="AA9">
+        <v>3.6</v>
+      </c>
+      <c r="AB9">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10">
+        <v>8240.5834429999995</v>
+      </c>
+      <c r="E10">
+        <v>215</v>
+      </c>
+      <c r="F10">
+        <v>249</v>
+      </c>
+      <c r="G10">
+        <v>234</v>
+      </c>
+      <c r="H10">
+        <v>303</v>
+      </c>
+      <c r="I10">
+        <v>254.7</v>
+      </c>
+      <c r="J10">
+        <v>262.8</v>
+      </c>
+      <c r="K10">
+        <v>257.39999999999998</v>
+      </c>
+      <c r="L10">
+        <v>266.08344299999999</v>
+      </c>
+      <c r="M10">
+        <v>424.2</v>
+      </c>
+      <c r="N10">
+        <v>606.20000000000005</v>
+      </c>
+      <c r="O10">
+        <v>599.20000000000005</v>
+      </c>
+      <c r="P10">
+        <v>439</v>
+      </c>
+      <c r="Q10">
+        <v>410</v>
+      </c>
+      <c r="R10">
+        <v>401</v>
+      </c>
+      <c r="S10">
+        <v>356</v>
+      </c>
+      <c r="T10">
+        <v>295</v>
+      </c>
+      <c r="U10">
+        <v>424.2</v>
+      </c>
+      <c r="V10">
+        <v>401.8</v>
+      </c>
+      <c r="W10">
+        <v>401.8</v>
+      </c>
+      <c r="X10">
+        <v>429.8</v>
+      </c>
+      <c r="Y10">
+        <v>303</v>
+      </c>
+      <c r="Z10">
+        <v>271.8</v>
+      </c>
+      <c r="AA10">
+        <v>220.5</v>
+      </c>
+      <c r="AB10">
+        <v>215.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11">
+        <v>458.31698929999999</v>
+      </c>
+      <c r="E11">
+        <v>34</v>
+      </c>
+      <c r="F11">
+        <v>37</v>
+      </c>
+      <c r="G11">
+        <v>35</v>
+      </c>
+      <c r="H11">
+        <v>37</v>
+      </c>
+      <c r="I11">
+        <v>19.8</v>
+      </c>
+      <c r="J11">
+        <v>18</v>
+      </c>
+      <c r="K11">
+        <v>11.7</v>
+      </c>
+      <c r="L11">
+        <v>5.1169892890000002</v>
+      </c>
+      <c r="M11">
+        <v>8.4</v>
+      </c>
+      <c r="N11">
+        <v>15.4</v>
+      </c>
+      <c r="O11">
+        <v>18.2</v>
+      </c>
+      <c r="P11">
+        <v>9</v>
+      </c>
+      <c r="Q11">
+        <v>16</v>
+      </c>
+      <c r="R11">
+        <v>11</v>
+      </c>
+      <c r="S11">
+        <v>12</v>
+      </c>
+      <c r="T11">
+        <v>5</v>
+      </c>
+      <c r="U11">
+        <v>11.2</v>
+      </c>
+      <c r="V11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="X11">
+        <v>21</v>
+      </c>
+      <c r="Y11">
+        <v>23</v>
+      </c>
+      <c r="Z11">
+        <v>25.2</v>
+      </c>
+      <c r="AA11">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="AB11">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12">
+        <v>84833.873340000006</v>
+      </c>
+      <c r="E12">
+        <v>861.79310339999995</v>
+      </c>
+      <c r="F12">
+        <v>559.35632180000005</v>
+      </c>
+      <c r="G12">
+        <v>436.96551720000002</v>
+      </c>
+      <c r="H12">
+        <v>837.51724139999999</v>
+      </c>
+      <c r="I12">
+        <v>1433.988662</v>
+      </c>
+      <c r="J12">
+        <v>2268.5793100000001</v>
+      </c>
+      <c r="K12">
+        <v>3232.6344829999998</v>
+      </c>
+      <c r="L12">
+        <v>2406.951724</v>
+      </c>
+      <c r="M12">
+        <v>2336.5517239999999</v>
+      </c>
+      <c r="N12">
+        <v>2483.4206899999999</v>
+      </c>
+      <c r="O12">
+        <v>2834.8137929999998</v>
+      </c>
+      <c r="P12">
+        <v>4759.2827589999997</v>
+      </c>
+      <c r="Q12">
+        <v>5000.5241379999998</v>
+      </c>
+      <c r="R12">
+        <v>5282.7310340000004</v>
+      </c>
+      <c r="S12">
+        <v>5573.131034</v>
+      </c>
+      <c r="T12">
+        <v>5948.6319450000001</v>
+      </c>
+      <c r="U12">
+        <v>7289.2281549999998</v>
+      </c>
+      <c r="V12">
+        <v>7454.2911029999996</v>
+      </c>
+      <c r="W12">
+        <v>7717.3312500000002</v>
+      </c>
+      <c r="X12">
+        <v>5598.0252110000001</v>
+      </c>
+      <c r="Y12">
+        <v>3418.3448279999998</v>
+      </c>
+      <c r="Z12">
+        <v>3129.7655169999998</v>
+      </c>
+      <c r="AA12">
+        <v>2371.4482760000001</v>
+      </c>
+      <c r="AB12">
+        <v>1598.565517</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13">
+        <v>1401.5491770000001</v>
+      </c>
+      <c r="E13">
+        <v>13.5</v>
+      </c>
+      <c r="F13">
+        <v>12.75</v>
+      </c>
+      <c r="G13">
+        <v>13.5</v>
+      </c>
+      <c r="H13">
+        <v>18.75</v>
+      </c>
+      <c r="I13">
+        <v>17.161550909999999</v>
+      </c>
+      <c r="J13">
+        <v>36.450000000000003</v>
+      </c>
+      <c r="K13">
+        <v>62.774999999999999</v>
+      </c>
+      <c r="L13">
+        <v>56.25</v>
+      </c>
+      <c r="M13">
+        <v>57.6</v>
+      </c>
+      <c r="N13">
+        <v>65.25</v>
+      </c>
+      <c r="O13">
+        <v>77.849999999999994</v>
+      </c>
+      <c r="P13">
+        <v>115.425</v>
+      </c>
+      <c r="Q13">
+        <v>122.175</v>
+      </c>
+      <c r="R13">
+        <v>135.67500000000001</v>
+      </c>
+      <c r="S13">
+        <v>106.65</v>
+      </c>
+      <c r="T13">
+        <v>93.205136179999997</v>
+      </c>
+      <c r="U13">
+        <v>108.4295697</v>
+      </c>
+      <c r="V13">
+        <v>85.033652849999996</v>
+      </c>
+      <c r="W13">
+        <v>101.2000772</v>
+      </c>
+      <c r="X13">
+        <v>31.719190149999999</v>
+      </c>
+      <c r="Y13">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="Z13">
+        <v>22.274999999999999</v>
+      </c>
+      <c r="AA13">
+        <v>16.2</v>
+      </c>
+      <c r="AB13">
+        <v>12.824999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14">
+        <v>413.9355683</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14">
+        <v>7</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>3.9794900659999999</v>
+      </c>
+      <c r="J14">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="K14">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="L14">
+        <v>25.8</v>
+      </c>
+      <c r="M14">
+        <v>19.8</v>
+      </c>
+      <c r="N14">
+        <v>22.2</v>
+      </c>
+      <c r="O14">
+        <v>31.2</v>
+      </c>
+      <c r="P14">
+        <v>27.9</v>
+      </c>
+      <c r="Q14">
+        <v>35.1</v>
+      </c>
+      <c r="R14">
+        <v>28.8</v>
+      </c>
+      <c r="S14">
+        <v>19.8</v>
+      </c>
+      <c r="T14">
+        <v>30.834781889999999</v>
+      </c>
+      <c r="U14">
+        <v>14.45727596</v>
+      </c>
+      <c r="V14">
+        <v>25.71464417</v>
+      </c>
+      <c r="W14">
+        <v>26.200667249999999</v>
+      </c>
+      <c r="X14">
+        <v>7.0487089210000002</v>
+      </c>
+      <c r="Y14">
+        <v>0.9</v>
+      </c>
+      <c r="Z14">
+        <v>8.1</v>
+      </c>
+      <c r="AA14">
+        <v>2.7</v>
+      </c>
+      <c r="AB14">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15">
+        <v>3581.8908200000001</v>
+      </c>
+      <c r="E15">
+        <v>121</v>
+      </c>
+      <c r="F15">
+        <v>108</v>
+      </c>
+      <c r="G15">
+        <v>104</v>
+      </c>
+      <c r="H15">
+        <v>97</v>
+      </c>
+      <c r="I15">
+        <v>122.3693195</v>
+      </c>
+      <c r="J15">
+        <v>146.69999999999999</v>
+      </c>
+      <c r="K15">
+        <v>153.9</v>
+      </c>
+      <c r="L15">
+        <v>96.6</v>
+      </c>
+      <c r="M15">
+        <v>105</v>
+      </c>
+      <c r="N15">
+        <v>150.6</v>
+      </c>
+      <c r="O15">
+        <v>189</v>
+      </c>
+      <c r="P15">
+        <v>253.8</v>
+      </c>
+      <c r="Q15">
+        <v>230.4</v>
+      </c>
+      <c r="R15">
+        <v>222.3</v>
+      </c>
+      <c r="S15">
+        <v>171.9</v>
+      </c>
+      <c r="T15">
+        <v>159.78023339999999</v>
+      </c>
+      <c r="U15">
+        <v>144.57275960000001</v>
+      </c>
+      <c r="V15">
+        <v>187.01559399999999</v>
+      </c>
+      <c r="W15">
+        <v>222.70567159999999</v>
+      </c>
+      <c r="X15">
+        <v>151.54724179999999</v>
+      </c>
+      <c r="Y15">
+        <v>136.80000000000001</v>
+      </c>
+      <c r="Z15">
+        <v>109.8</v>
+      </c>
+      <c r="AA15">
+        <v>103.5</v>
+      </c>
+      <c r="AB15">
+        <v>93.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16">
+        <v>208.35007659999999</v>
+      </c>
+      <c r="E16">
+        <v>9</v>
+      </c>
+      <c r="F16">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>14</v>
+      </c>
+      <c r="H16">
+        <v>13</v>
+      </c>
+      <c r="I16">
+        <v>12.933342720000001</v>
+      </c>
+      <c r="J16">
+        <v>11.7</v>
+      </c>
+      <c r="K16">
+        <v>4.5</v>
+      </c>
+      <c r="L16">
+        <v>2.4</v>
+      </c>
+      <c r="M16">
+        <v>3.6</v>
+      </c>
+      <c r="N16">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="O16">
+        <v>6.6</v>
+      </c>
+      <c r="P16">
+        <v>10.8</v>
+      </c>
+      <c r="Q16">
+        <v>13.5</v>
+      </c>
+      <c r="R16">
+        <v>8.1</v>
+      </c>
+      <c r="S16">
+        <v>9</v>
+      </c>
+      <c r="T16">
+        <v>2.80316199</v>
+      </c>
+      <c r="U16">
+        <v>2.2241963010000001</v>
+      </c>
+      <c r="V16">
+        <v>3.5065423870000001</v>
+      </c>
+      <c r="W16">
+        <v>7.8602001760000002</v>
+      </c>
+      <c r="X16">
+        <v>12.922633019999999</v>
+      </c>
+      <c r="Y16">
+        <v>8.1</v>
+      </c>
+      <c r="Z16">
+        <v>10.8</v>
+      </c>
+      <c r="AA16">
+        <v>11.7</v>
+      </c>
+      <c r="AB16">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17">
+        <v>95951.50894</v>
+      </c>
+      <c r="E17">
+        <v>839.54022989999999</v>
+      </c>
+      <c r="F17">
+        <v>521.93103450000001</v>
+      </c>
+      <c r="G17">
+        <v>369.19540230000001</v>
+      </c>
+      <c r="H17">
+        <v>571.49425289999999</v>
+      </c>
+      <c r="I17">
+        <v>1394.8505749999999</v>
+      </c>
+      <c r="J17">
+        <v>3574.0137930000001</v>
+      </c>
+      <c r="K17">
+        <v>5361.0206900000003</v>
+      </c>
+      <c r="L17">
+        <v>7452.8919539999997</v>
+      </c>
+      <c r="M17">
+        <v>6225.14023</v>
+      </c>
+      <c r="N17">
+        <v>6366.749425</v>
+      </c>
+      <c r="O17">
+        <v>6440.3862069999996</v>
+      </c>
+      <c r="P17">
+        <v>4735.816092</v>
+      </c>
+      <c r="Q17">
+        <v>4594.3637419999995</v>
+      </c>
+      <c r="R17">
+        <v>4985.6551719999998</v>
+      </c>
+      <c r="S17">
+        <v>5249.6551719999998</v>
+      </c>
+      <c r="T17">
+        <v>4856.183908</v>
+      </c>
+      <c r="U17">
+        <v>6061.6127509999997</v>
+      </c>
+      <c r="V17">
+        <v>5504.5576440000004</v>
+      </c>
+      <c r="W17">
+        <v>6523.9356319999997</v>
+      </c>
+      <c r="X17">
+        <v>4369.5901629999998</v>
+      </c>
+      <c r="Y17">
+        <v>3218.9793100000002</v>
+      </c>
+      <c r="Z17">
+        <v>3039.6413790000001</v>
+      </c>
+      <c r="AA17">
+        <v>2148.4137930000002</v>
+      </c>
+      <c r="AB17">
+        <v>1545.8903849999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18">
+        <v>1558.311416</v>
+      </c>
+      <c r="E18">
+        <v>12.75</v>
+      </c>
+      <c r="F18">
+        <v>19.5</v>
+      </c>
+      <c r="G18">
+        <v>22.5</v>
+      </c>
+      <c r="H18">
+        <v>13.5</v>
+      </c>
+      <c r="I18">
+        <v>22.5</v>
+      </c>
+      <c r="J18">
+        <v>25.65</v>
+      </c>
+      <c r="K18">
+        <v>57.375</v>
+      </c>
+      <c r="L18">
+        <v>98.7</v>
+      </c>
+      <c r="M18">
+        <v>132.30000000000001</v>
+      </c>
+      <c r="N18">
+        <v>198.45</v>
+      </c>
+      <c r="O18">
+        <v>129.15</v>
+      </c>
+      <c r="P18">
+        <v>111.75</v>
+      </c>
+      <c r="Q18">
+        <v>96.706678949999997</v>
+      </c>
+      <c r="R18">
+        <v>102</v>
+      </c>
+      <c r="S18">
+        <v>115.5</v>
+      </c>
+      <c r="T18">
+        <v>80.25</v>
+      </c>
+      <c r="U18">
+        <v>79.956381449999995</v>
+      </c>
+      <c r="V18">
+        <v>70.839430370000002</v>
+      </c>
+      <c r="W18">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="X18">
+        <v>34.370068570000001</v>
+      </c>
+      <c r="Y18">
+        <v>18.225000000000001</v>
+      </c>
+      <c r="Z18">
+        <v>21.6</v>
+      </c>
+      <c r="AA18">
+        <v>8.7750000000000004</v>
+      </c>
+      <c r="AB18">
+        <v>10.363857019999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19">
+        <v>558.91958109999996</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>27.9</v>
+      </c>
+      <c r="K19">
+        <v>51.3</v>
+      </c>
+      <c r="L19">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="M19">
+        <v>42</v>
+      </c>
+      <c r="N19">
+        <v>65.8</v>
+      </c>
+      <c r="O19">
+        <v>60.2</v>
+      </c>
+      <c r="P19">
+        <v>31</v>
+      </c>
+      <c r="Q19">
+        <v>33.882632049999998</v>
+      </c>
+      <c r="R19">
+        <v>33</v>
+      </c>
+      <c r="S19">
+        <v>40</v>
+      </c>
+      <c r="T19">
+        <v>27</v>
+      </c>
+      <c r="U19">
+        <v>33.315158930000003</v>
+      </c>
+      <c r="V19">
+        <v>26.35885781</v>
+      </c>
+      <c r="W19">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="X19">
+        <v>12.220468820000001</v>
+      </c>
+      <c r="Y19">
+        <v>5.4</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>2.7</v>
+      </c>
+      <c r="AB19">
+        <v>1.84246347</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20">
+        <v>3840.382059</v>
+      </c>
+      <c r="E20">
+        <v>95</v>
+      </c>
+      <c r="F20">
+        <v>110</v>
+      </c>
+      <c r="G20">
+        <v>100</v>
+      </c>
+      <c r="H20">
+        <v>133</v>
+      </c>
+      <c r="I20">
+        <v>111</v>
+      </c>
+      <c r="J20">
+        <v>123.3</v>
+      </c>
+      <c r="K20">
+        <v>126.9</v>
+      </c>
+      <c r="L20">
+        <v>141.4</v>
+      </c>
+      <c r="M20">
+        <v>260.39999999999998</v>
+      </c>
+      <c r="N20">
+        <v>253.4</v>
+      </c>
+      <c r="O20">
+        <v>296.8</v>
+      </c>
+      <c r="P20">
+        <v>210</v>
+      </c>
+      <c r="Q20">
+        <v>211.7664503</v>
+      </c>
+      <c r="R20">
+        <v>188</v>
+      </c>
+      <c r="S20">
+        <v>197</v>
+      </c>
+      <c r="T20">
+        <v>155</v>
+      </c>
+      <c r="U20">
+        <v>193.22792179999999</v>
+      </c>
+      <c r="V20">
+        <v>164.74286129999999</v>
+      </c>
+      <c r="W20">
+        <v>184.8</v>
+      </c>
+      <c r="X20">
+        <v>163.95795670000001</v>
+      </c>
+      <c r="Y20">
+        <v>131.4</v>
+      </c>
+      <c r="Z20">
+        <v>108.9</v>
+      </c>
+      <c r="AA20">
+        <v>85.5</v>
+      </c>
+      <c r="AB20">
+        <v>94.886868730000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21">
+        <v>192.2115622</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+      <c r="F21">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>14</v>
+      </c>
+      <c r="H21">
+        <v>13</v>
+      </c>
+      <c r="I21">
+        <v>9</v>
+      </c>
+      <c r="J21">
+        <v>9.9</v>
+      </c>
+      <c r="K21">
+        <v>4.5</v>
+      </c>
+      <c r="L21">
+        <v>5.6</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>5.6</v>
+      </c>
+      <c r="O21">
+        <v>4.2</v>
+      </c>
+      <c r="P21">
+        <v>6</v>
+      </c>
+      <c r="Q21">
+        <v>8.4706580129999995</v>
+      </c>
+      <c r="R21">
+        <v>10</v>
+      </c>
+      <c r="S21">
+        <v>14</v>
+      </c>
+      <c r="T21">
+        <v>5</v>
+      </c>
+      <c r="U21">
+        <v>3.997819072</v>
+      </c>
+      <c r="V21">
+        <v>4.3931429690000003</v>
+      </c>
+      <c r="W21">
+        <v>5.6</v>
+      </c>
+      <c r="X21">
+        <v>6.1102344119999996</v>
+      </c>
+      <c r="Y21">
+        <v>7.2</v>
+      </c>
+      <c r="Z21">
+        <v>5.4</v>
+      </c>
+      <c r="AA21">
+        <v>13.5</v>
+      </c>
+      <c r="AB21">
+        <v>14.73970776</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22">
+        <v>91231.694140000007</v>
+      </c>
+      <c r="E22">
+        <v>1128.8275860000001</v>
+      </c>
+      <c r="F22">
+        <v>868.87356320000004</v>
+      </c>
+      <c r="G22">
+        <v>668.59770109999999</v>
+      </c>
+      <c r="H22">
+        <v>598.80459770000004</v>
+      </c>
+      <c r="I22">
+        <v>986.07574899999997</v>
+      </c>
+      <c r="J22">
+        <v>2722.841379</v>
+      </c>
+      <c r="K22">
+        <v>3953.6275860000001</v>
+      </c>
+      <c r="L22">
+        <v>6087.7793099999999</v>
+      </c>
+      <c r="M22">
+        <v>5723.8436780000002</v>
+      </c>
+      <c r="N22">
+        <v>5916.4321840000002</v>
+      </c>
+      <c r="O22">
+        <v>6376.662069</v>
+      </c>
+      <c r="P22">
+        <v>4872.3678159999999</v>
+      </c>
+      <c r="Q22">
+        <v>4783.3563219999996</v>
+      </c>
+      <c r="R22">
+        <v>4781.3333329999996</v>
+      </c>
+      <c r="S22">
+        <v>4996.7816089999997</v>
+      </c>
+      <c r="T22">
+        <v>3930.666667</v>
+      </c>
+      <c r="U22">
+        <v>4885.5172409999996</v>
+      </c>
+      <c r="V22">
+        <v>5045.5356320000001</v>
+      </c>
+      <c r="W22">
+        <v>5764.9103450000002</v>
+      </c>
+      <c r="X22">
+        <v>6035.3839079999998</v>
+      </c>
+      <c r="Y22">
+        <v>3500.275862</v>
+      </c>
+      <c r="Z22">
+        <v>3152.5241380000002</v>
+      </c>
+      <c r="AA22">
+        <v>2572.6344829999998</v>
+      </c>
+      <c r="AB22">
+        <v>1878.041379</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23">
+        <v>2165.8825790000001</v>
+      </c>
+      <c r="E23">
+        <v>21</v>
+      </c>
+      <c r="F23">
+        <v>15</v>
+      </c>
+      <c r="G23">
+        <v>15</v>
+      </c>
+      <c r="H23">
+        <v>31.5</v>
+      </c>
+      <c r="I23">
+        <v>39.632579360000001</v>
+      </c>
+      <c r="J23">
+        <v>72.900000000000006</v>
+      </c>
+      <c r="K23">
+        <v>108</v>
+      </c>
+      <c r="L23">
+        <v>232.05</v>
+      </c>
+      <c r="M23">
+        <v>255.15</v>
+      </c>
+      <c r="N23">
+        <v>292.95</v>
+      </c>
+      <c r="O23">
+        <v>190.05</v>
+      </c>
+      <c r="P23">
+        <v>132.75</v>
+      </c>
+      <c r="Q23">
+        <v>130.5</v>
+      </c>
+      <c r="R23">
+        <v>114.75</v>
+      </c>
+      <c r="S23">
+        <v>101.25</v>
+      </c>
+      <c r="T23">
+        <v>52.5</v>
+      </c>
+      <c r="U23">
+        <v>67.2</v>
+      </c>
+      <c r="V23">
+        <v>73.5</v>
+      </c>
+      <c r="W23">
+        <v>89.25</v>
+      </c>
+      <c r="X23">
+        <v>47.25</v>
+      </c>
+      <c r="Y23">
+        <v>23.625</v>
+      </c>
+      <c r="Z23">
+        <v>21.6</v>
+      </c>
+      <c r="AA23">
+        <v>18.225000000000001</v>
+      </c>
+      <c r="AB23">
+        <v>20.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24">
+        <v>908.52187560000004</v>
+      </c>
+      <c r="E24">
+        <v>6</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>11</v>
+      </c>
+      <c r="H24">
+        <v>6</v>
+      </c>
+      <c r="I24">
+        <v>18.221875570000002</v>
+      </c>
+      <c r="J24">
+        <v>45.9</v>
+      </c>
+      <c r="K24">
+        <v>70.2</v>
+      </c>
+      <c r="L24">
+        <v>119</v>
+      </c>
+      <c r="M24">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="N24">
+        <v>99.4</v>
+      </c>
+      <c r="O24">
+        <v>81.2</v>
+      </c>
+      <c r="P24">
+        <v>73</v>
+      </c>
+      <c r="Q24">
+        <v>74</v>
+      </c>
+      <c r="R24">
+        <v>53</v>
+      </c>
+      <c r="S24">
+        <v>41</v>
+      </c>
+      <c r="T24">
+        <v>22</v>
+      </c>
+      <c r="U24">
+        <v>21</v>
+      </c>
+      <c r="V24">
+        <v>33.6</v>
+      </c>
+      <c r="W24">
+        <v>22.4</v>
+      </c>
+      <c r="X24">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="Y24">
+        <v>4.5</v>
+      </c>
+      <c r="Z24">
+        <v>2.7</v>
+      </c>
+      <c r="AA24">
+        <v>4.5</v>
+      </c>
+      <c r="AB24">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25">
+        <v>7012.0403189999997</v>
+      </c>
+      <c r="E25">
+        <v>179</v>
+      </c>
+      <c r="F25">
+        <v>156</v>
+      </c>
+      <c r="G25">
+        <v>183</v>
+      </c>
+      <c r="H25">
+        <v>177</v>
+      </c>
+      <c r="I25">
+        <v>216.84031920000001</v>
+      </c>
+      <c r="J25">
+        <v>225.9</v>
+      </c>
+      <c r="K25">
+        <v>193.5</v>
+      </c>
+      <c r="L25">
+        <v>315</v>
+      </c>
+      <c r="M25">
+        <v>422.8</v>
+      </c>
+      <c r="N25">
+        <v>480.2</v>
+      </c>
+      <c r="O25">
+        <v>590.79999999999995</v>
+      </c>
+      <c r="P25">
+        <v>405</v>
+      </c>
+      <c r="Q25">
+        <v>385</v>
+      </c>
+      <c r="R25">
+        <v>369</v>
+      </c>
+      <c r="S25">
+        <v>306</v>
+      </c>
+      <c r="T25">
+        <v>262</v>
+      </c>
+      <c r="U25">
+        <v>292.60000000000002</v>
+      </c>
+      <c r="V25">
+        <v>322</v>
+      </c>
+      <c r="W25">
+        <v>351.4</v>
+      </c>
+      <c r="X25">
+        <v>415.8</v>
+      </c>
+      <c r="Y25">
+        <v>228.6</v>
+      </c>
+      <c r="Z25">
+        <v>188.1</v>
+      </c>
+      <c r="AA25">
+        <v>179.1</v>
+      </c>
+      <c r="AB25">
+        <v>167.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26">
+        <v>400.06625070000001</v>
+      </c>
+      <c r="E26">
+        <v>30</v>
+      </c>
+      <c r="F26">
+        <v>29</v>
+      </c>
+      <c r="G26">
+        <v>20</v>
+      </c>
+      <c r="H26">
+        <v>19</v>
+      </c>
+      <c r="I26">
+        <v>21.86625068</v>
+      </c>
+      <c r="J26">
+        <v>22.5</v>
+      </c>
+      <c r="K26">
+        <v>10.8</v>
+      </c>
+      <c r="L26">
+        <v>18.2</v>
+      </c>
+      <c r="M26">
+        <v>5.6</v>
+      </c>
+      <c r="N26">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="O26">
+        <v>14</v>
+      </c>
+      <c r="P26">
+        <v>11</v>
+      </c>
+      <c r="Q26">
+        <v>13</v>
+      </c>
+      <c r="R26">
+        <v>11</v>
+      </c>
+      <c r="S26">
+        <v>8</v>
+      </c>
+      <c r="T26">
+        <v>2</v>
+      </c>
+      <c r="U26">
+        <v>7</v>
+      </c>
+      <c r="V26">
+        <v>5.6</v>
+      </c>
+      <c r="W26">
+        <v>22.4</v>
+      </c>
+      <c r="X26">
+        <v>29.4</v>
+      </c>
+      <c r="Y26">
+        <v>18</v>
+      </c>
+      <c r="Z26">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="AA26">
+        <v>23.4</v>
+      </c>
+      <c r="AB26">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27">
+        <v>63817.298580000002</v>
+      </c>
+      <c r="E27">
+        <v>526.98850570000002</v>
+      </c>
+      <c r="F27">
+        <v>362.11494249999998</v>
+      </c>
+      <c r="G27">
+        <v>354.5287356</v>
+      </c>
+      <c r="H27">
+        <v>540.64367819999995</v>
+      </c>
+      <c r="I27">
+        <v>1107.8916850000001</v>
+      </c>
+      <c r="J27">
+        <v>2760.1655169999999</v>
+      </c>
+      <c r="K27">
+        <v>3188.2298850000002</v>
+      </c>
+      <c r="L27">
+        <v>4101.7103450000004</v>
+      </c>
+      <c r="M27">
+        <v>3564.3034480000001</v>
+      </c>
+      <c r="N27">
+        <v>3794.4183910000002</v>
+      </c>
+      <c r="O27">
+        <v>4223.4942529999998</v>
+      </c>
+      <c r="P27">
+        <v>3094.1609199999998</v>
+      </c>
+      <c r="Q27">
+        <v>3098.206897</v>
+      </c>
+      <c r="R27">
+        <v>3214.0229890000001</v>
+      </c>
+      <c r="S27">
+        <v>3444.1379310000002</v>
+      </c>
+      <c r="T27">
+        <v>3366.7586209999999</v>
+      </c>
+      <c r="U27">
+        <v>3987.7149429999999</v>
+      </c>
+      <c r="V27">
+        <v>4588.8459769999999</v>
+      </c>
+      <c r="W27">
+        <v>4413.9586209999998</v>
+      </c>
+      <c r="X27">
+        <v>3752.6436779999999</v>
+      </c>
+      <c r="Y27">
+        <v>2007.765517</v>
+      </c>
+      <c r="Z27">
+        <v>1829.337931</v>
+      </c>
+      <c r="AA27">
+        <v>1534.841379</v>
+      </c>
+      <c r="AB27">
+        <v>960.41379310000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28">
+        <v>1466.12761</v>
+      </c>
+      <c r="E28">
+        <v>9.75</v>
+      </c>
+      <c r="F28">
+        <v>12.375</v>
+      </c>
+      <c r="G28">
+        <v>13.875</v>
+      </c>
+      <c r="H28">
+        <v>19.875</v>
+      </c>
+      <c r="I28">
+        <v>27.777609519999999</v>
+      </c>
+      <c r="J28">
+        <v>38.475000000000001</v>
+      </c>
+      <c r="K28">
+        <v>59.25</v>
+      </c>
+      <c r="L28">
+        <v>105</v>
+      </c>
+      <c r="M28">
+        <v>127.575</v>
+      </c>
+      <c r="N28">
+        <v>155.4</v>
+      </c>
+      <c r="O28">
+        <v>133.875</v>
+      </c>
+      <c r="P28">
+        <v>81</v>
+      </c>
+      <c r="Q28">
+        <v>96</v>
+      </c>
+      <c r="R28">
+        <v>87.75</v>
+      </c>
+      <c r="S28">
+        <v>85.875</v>
+      </c>
+      <c r="T28">
+        <v>63.75</v>
+      </c>
+      <c r="U28">
+        <v>77.7</v>
+      </c>
+      <c r="V28">
+        <v>75.075000000000003</v>
+      </c>
+      <c r="W28">
+        <v>84</v>
+      </c>
+      <c r="X28">
+        <v>39.375</v>
+      </c>
+      <c r="Y28">
+        <v>24.975000000000001</v>
+      </c>
+      <c r="Z28">
+        <v>15.1875</v>
+      </c>
+      <c r="AA28">
+        <v>17.212499999999999</v>
+      </c>
+      <c r="AB28">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29">
+        <v>450.55118670000002</v>
+      </c>
+      <c r="E29">
+        <v>4.5</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29">
+        <v>1.5</v>
+      </c>
+      <c r="H29">
+        <v>0.5</v>
+      </c>
+      <c r="I29">
+        <v>7.901186708</v>
+      </c>
+      <c r="J29">
+        <v>16.649999999999999</v>
+      </c>
+      <c r="K29">
+        <v>31</v>
+      </c>
+      <c r="L29">
+        <v>28.7</v>
+      </c>
+      <c r="M29">
+        <v>29.4</v>
+      </c>
+      <c r="N29">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="O29">
+        <v>44.8</v>
+      </c>
+      <c r="P29">
+        <v>31</v>
+      </c>
+      <c r="Q29">
+        <v>35</v>
+      </c>
+      <c r="R29">
+        <v>24</v>
+      </c>
+      <c r="S29">
+        <v>24.5</v>
+      </c>
+      <c r="T29">
+        <v>27.5</v>
+      </c>
+      <c r="U29">
+        <v>25.9</v>
+      </c>
+      <c r="V29">
+        <v>26.6</v>
+      </c>
+      <c r="W29">
+        <v>20.3</v>
+      </c>
+      <c r="X29">
+        <v>11.2</v>
+      </c>
+      <c r="Y29">
+        <v>2.7</v>
+      </c>
+      <c r="Z29">
+        <v>6.3</v>
+      </c>
+      <c r="AA29">
+        <v>0.9</v>
+      </c>
+      <c r="AB29">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30">
+        <v>5888.1802610000004</v>
+      </c>
+      <c r="E30">
+        <v>157.5</v>
+      </c>
+      <c r="F30">
+        <v>160.5</v>
+      </c>
+      <c r="G30">
+        <v>145</v>
+      </c>
+      <c r="H30">
+        <v>193.5</v>
+      </c>
+      <c r="I30">
+        <v>201.48026110000001</v>
+      </c>
+      <c r="J30">
+        <v>171.9</v>
+      </c>
+      <c r="K30">
+        <v>161</v>
+      </c>
+      <c r="L30">
+        <v>218.4</v>
+      </c>
+      <c r="M30">
+        <v>312.2</v>
+      </c>
+      <c r="N30">
+        <v>494.9</v>
+      </c>
+      <c r="O30">
+        <v>466.9</v>
+      </c>
+      <c r="P30">
+        <v>304.5</v>
+      </c>
+      <c r="Q30">
+        <v>315</v>
+      </c>
+      <c r="R30">
+        <v>306.5</v>
+      </c>
+      <c r="S30">
+        <v>237.5</v>
+      </c>
+      <c r="T30">
+        <v>222.5</v>
+      </c>
+      <c r="U30">
+        <v>297.5</v>
+      </c>
+      <c r="V30">
+        <v>270.2</v>
+      </c>
+      <c r="W30">
+        <v>278.60000000000002</v>
+      </c>
+      <c r="X30">
+        <v>265.3</v>
+      </c>
+      <c r="Y30">
+        <v>180</v>
+      </c>
+      <c r="Z30">
+        <v>185.85</v>
+      </c>
+      <c r="AA30">
+        <v>166.95</v>
+      </c>
+      <c r="AB30">
+        <v>174.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31">
+        <v>376.20973600000002</v>
+      </c>
+      <c r="E31">
+        <v>27.5</v>
+      </c>
+      <c r="F31">
+        <v>28</v>
+      </c>
+      <c r="G31">
+        <v>36.5</v>
+      </c>
+      <c r="H31">
+        <v>31</v>
+      </c>
+      <c r="I31">
+        <v>23.20973596</v>
+      </c>
+      <c r="J31">
+        <v>14.85</v>
+      </c>
+      <c r="K31">
+        <v>9</v>
+      </c>
+      <c r="L31">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="M31">
+        <v>11.9</v>
+      </c>
+      <c r="N31">
+        <v>6.3</v>
+      </c>
+      <c r="O31">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="P31">
+        <v>7</v>
+      </c>
+      <c r="Q31">
+        <v>17.5</v>
+      </c>
+      <c r="R31">
+        <v>6.5</v>
+      </c>
+      <c r="S31">
+        <v>7.5</v>
+      </c>
+      <c r="T31">
+        <v>2.5</v>
+      </c>
+      <c r="U31">
+        <v>7.7</v>
+      </c>
+      <c r="V31">
+        <v>5.6</v>
+      </c>
+      <c r="W31">
+        <v>7</v>
+      </c>
+      <c r="X31">
+        <v>13.3</v>
+      </c>
+      <c r="Y31">
+        <v>14.85</v>
+      </c>
+      <c r="Z31">
+        <v>20.25</v>
+      </c>
+      <c r="AA31">
+        <v>33.75</v>
+      </c>
+      <c r="AB31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32">
+        <v>78695.812189999997</v>
+      </c>
+      <c r="E32">
+        <v>1116.6896549999999</v>
+      </c>
+      <c r="F32">
+        <v>838.5287356</v>
+      </c>
+      <c r="G32">
+        <v>701.9770115</v>
+      </c>
+      <c r="H32">
+        <v>588.68965519999995</v>
+      </c>
+      <c r="I32">
+        <v>889.10344829999997</v>
+      </c>
+      <c r="J32">
+        <v>2146.390805</v>
+      </c>
+      <c r="K32">
+        <v>3342.9885060000001</v>
+      </c>
+      <c r="L32">
+        <v>3797.2826100000002</v>
+      </c>
+      <c r="M32">
+        <v>3816.7839399999998</v>
+      </c>
+      <c r="N32">
+        <v>3512.6892429999998</v>
+      </c>
+      <c r="O32">
+        <v>3801.9299679999999</v>
+      </c>
+      <c r="P32">
+        <v>4112.7356319999999</v>
+      </c>
+      <c r="Q32">
+        <v>4065.6</v>
+      </c>
+      <c r="R32">
+        <v>4244.9379310000004</v>
+      </c>
+      <c r="S32">
+        <v>4518.9517239999996</v>
+      </c>
+      <c r="T32">
+        <v>3618.114943</v>
+      </c>
+      <c r="U32">
+        <v>4714.1701149999999</v>
+      </c>
+      <c r="V32">
+        <v>4718.4183910000002</v>
+      </c>
+      <c r="W32">
+        <v>5432.1287359999997</v>
+      </c>
+      <c r="X32">
+        <v>6365.3333329999996</v>
+      </c>
+      <c r="Y32">
+        <v>3887.1724140000001</v>
+      </c>
+      <c r="Z32">
+        <v>3476.5057470000002</v>
+      </c>
+      <c r="AA32">
+        <v>2884.7816090000001</v>
+      </c>
+      <c r="AB32">
+        <v>2103.908046</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33">
+        <v>2019.7622060000001</v>
+      </c>
+      <c r="E33">
+        <v>17.25</v>
+      </c>
+      <c r="F33">
+        <v>8.25</v>
+      </c>
+      <c r="G33">
+        <v>13.5</v>
+      </c>
+      <c r="H33">
+        <v>26.25</v>
+      </c>
+      <c r="I33">
+        <v>55.5</v>
+      </c>
+      <c r="J33">
+        <v>102</v>
+      </c>
+      <c r="K33">
+        <v>120</v>
+      </c>
+      <c r="L33">
+        <v>143.6604389</v>
+      </c>
+      <c r="M33">
+        <v>160.20733730000001</v>
+      </c>
+      <c r="N33">
+        <v>174.43148640000001</v>
+      </c>
+      <c r="O33">
+        <v>121.8629431</v>
+      </c>
+      <c r="P33">
+        <v>137.25</v>
+      </c>
+      <c r="Q33">
+        <v>155.25</v>
+      </c>
+      <c r="R33">
+        <v>147.15</v>
+      </c>
+      <c r="S33">
+        <v>114.75</v>
+      </c>
+      <c r="T33">
+        <v>80.25</v>
+      </c>
+      <c r="U33">
+        <v>80.849999999999994</v>
+      </c>
+      <c r="V33">
+        <v>86.1</v>
+      </c>
+      <c r="W33">
+        <v>108.15</v>
+      </c>
+      <c r="X33">
+        <v>80.849999999999994</v>
+      </c>
+      <c r="Y33">
+        <v>24</v>
+      </c>
+      <c r="Z33">
+        <v>30.75</v>
+      </c>
+      <c r="AA33">
+        <v>17.25</v>
+      </c>
+      <c r="AB33">
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34">
+        <v>852.2738693</v>
+      </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34">
+        <v>6</v>
+      </c>
+      <c r="G34">
+        <v>6</v>
+      </c>
+      <c r="H34">
+        <v>8</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>31</v>
+      </c>
+      <c r="K34">
+        <v>75</v>
+      </c>
+      <c r="L34">
+        <v>75.841043850000005</v>
+      </c>
+      <c r="M34">
+        <v>75.901953349999999</v>
+      </c>
+      <c r="N34">
+        <v>87.744323469999998</v>
+      </c>
+      <c r="O34">
+        <v>71.986548639999995</v>
+      </c>
+      <c r="P34">
+        <v>78</v>
+      </c>
+      <c r="Q34">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="R34">
+        <v>54.9</v>
+      </c>
+      <c r="S34">
+        <v>45</v>
+      </c>
+      <c r="T34">
+        <v>28</v>
+      </c>
+      <c r="U34">
+        <v>25.2</v>
+      </c>
+      <c r="V34">
+        <v>25.2</v>
+      </c>
+      <c r="W34">
+        <v>26.6</v>
+      </c>
+      <c r="X34">
+        <v>21</v>
+      </c>
+      <c r="Y34">
+        <v>6</v>
+      </c>
+      <c r="Z34">
+        <v>6</v>
+      </c>
+      <c r="AA34">
+        <v>4</v>
+      </c>
+      <c r="AB34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35">
+        <v>6957.4667900000004</v>
+      </c>
+      <c r="E35">
+        <v>188</v>
+      </c>
+      <c r="F35">
+        <v>179</v>
+      </c>
+      <c r="G35">
+        <v>173</v>
+      </c>
+      <c r="H35">
+        <v>198</v>
+      </c>
+      <c r="I35">
+        <v>254</v>
+      </c>
+      <c r="J35">
+        <v>263</v>
+      </c>
+      <c r="K35">
+        <v>234</v>
+      </c>
+      <c r="L35">
+        <v>266.4159745</v>
+      </c>
+      <c r="M35">
+        <v>344.81173100000001</v>
+      </c>
+      <c r="N35">
+        <v>398.54951740000001</v>
+      </c>
+      <c r="O35">
+        <v>438.08956740000002</v>
+      </c>
+      <c r="P35">
+        <v>435</v>
+      </c>
+      <c r="Q35">
+        <v>380.7</v>
+      </c>
+      <c r="R35">
+        <v>349.2</v>
+      </c>
+      <c r="S35">
+        <v>279.89999999999998</v>
+      </c>
+      <c r="T35">
+        <v>262</v>
+      </c>
+      <c r="U35">
+        <v>310.8</v>
+      </c>
+      <c r="V35">
+        <v>324.8</v>
+      </c>
+      <c r="W35">
+        <v>389.2</v>
+      </c>
+      <c r="X35">
+        <v>413</v>
+      </c>
+      <c r="Y35">
+        <v>239</v>
+      </c>
+      <c r="Z35">
+        <v>223</v>
+      </c>
+      <c r="AA35">
+        <v>218</v>
+      </c>
+      <c r="AB35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36">
+        <v>517.63055310000004</v>
+      </c>
+      <c r="E36">
+        <v>42</v>
+      </c>
+      <c r="F36">
+        <v>33</v>
+      </c>
+      <c r="G36">
+        <v>33</v>
+      </c>
+      <c r="H36">
+        <v>26</v>
+      </c>
+      <c r="I36">
+        <v>32</v>
+      </c>
+      <c r="J36">
+        <v>30</v>
+      </c>
+      <c r="K36">
+        <v>16</v>
+      </c>
+      <c r="L36">
+        <v>15.5571372</v>
+      </c>
+      <c r="M36">
+        <v>7.5901953349999998</v>
+      </c>
+      <c r="N36">
+        <v>23.257531520000001</v>
+      </c>
+      <c r="O36">
+        <v>15.425688989999999</v>
+      </c>
+      <c r="P36">
+        <v>17</v>
+      </c>
+      <c r="Q36">
+        <v>10.8</v>
+      </c>
+      <c r="R36">
+        <v>13.5</v>
+      </c>
+      <c r="S36">
+        <v>8.1</v>
+      </c>
+      <c r="T36">
+        <v>7</v>
+      </c>
+      <c r="U36">
+        <v>7</v>
+      </c>
+      <c r="V36">
+        <v>8.4</v>
+      </c>
+      <c r="W36">
+        <v>30.8</v>
+      </c>
+      <c r="X36">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="Y36">
+        <v>32</v>
+      </c>
+      <c r="Z36">
+        <v>20</v>
+      </c>
+      <c r="AA36">
+        <v>25</v>
+      </c>
+      <c r="AB36">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37">
+        <v>82108.534740000003</v>
+      </c>
+      <c r="E37">
+        <v>611.95402300000001</v>
+      </c>
+      <c r="F37">
+        <v>412.6896552</v>
+      </c>
+      <c r="G37">
+        <v>383.35632179999999</v>
+      </c>
+      <c r="H37">
+        <v>687.81609200000003</v>
+      </c>
+      <c r="I37">
+        <v>1436.524138</v>
+      </c>
+      <c r="J37">
+        <v>4678.2620690000003</v>
+      </c>
+      <c r="K37">
+        <v>5869.903448</v>
+      </c>
+      <c r="L37">
+        <v>5215.6455859999996</v>
+      </c>
+      <c r="M37">
+        <v>5848.5995380000004</v>
+      </c>
+      <c r="N37">
+        <v>5989.0084260000003</v>
+      </c>
+      <c r="O37">
+        <v>4845.8068510000003</v>
+      </c>
+      <c r="P37">
+        <v>3964.5517239999999</v>
+      </c>
+      <c r="Q37">
+        <v>4053.7655169999998</v>
+      </c>
+      <c r="R37">
+        <v>4194.868966</v>
+      </c>
+      <c r="S37">
+        <v>4498.9241380000003</v>
+      </c>
+      <c r="T37">
+        <v>4608.1655170000004</v>
+      </c>
+      <c r="U37">
+        <v>4168.251835</v>
+      </c>
+      <c r="V37">
+        <v>5308.5347339999998</v>
+      </c>
+      <c r="W37">
+        <v>5476.8441739999998</v>
+      </c>
+      <c r="X37">
+        <v>2793.3084869999998</v>
+      </c>
+      <c r="Y37">
+        <v>2211.227586</v>
+      </c>
+      <c r="Z37">
+        <v>2235.4022989999999</v>
+      </c>
+      <c r="AA37">
+        <v>1550.317241</v>
+      </c>
+      <c r="AB37">
+        <v>1064.806372</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38">
+        <v>1983.5044170000001</v>
+      </c>
+      <c r="E38">
+        <v>17.25</v>
+      </c>
+      <c r="F38">
+        <v>17.25</v>
+      </c>
+      <c r="G38">
+        <v>12.75</v>
+      </c>
+      <c r="H38">
+        <v>15.75</v>
+      </c>
+      <c r="I38">
+        <v>29.024999999999999</v>
+      </c>
+      <c r="J38">
+        <v>56.7</v>
+      </c>
+      <c r="K38">
+        <v>90.45</v>
+      </c>
+      <c r="L38">
+        <v>121.42752419999999</v>
+      </c>
+      <c r="M38">
+        <v>161.26063769999999</v>
+      </c>
+      <c r="N38">
+        <v>211.37464610000001</v>
+      </c>
+      <c r="O38">
+        <v>174.3322526</v>
+      </c>
+      <c r="P38">
+        <v>155.25</v>
+      </c>
+      <c r="Q38">
+        <v>154.57499999999999</v>
+      </c>
+      <c r="R38">
+        <v>139.05000000000001</v>
+      </c>
+      <c r="S38">
+        <v>137.02500000000001</v>
+      </c>
+      <c r="T38">
+        <v>87.075000000000003</v>
+      </c>
+      <c r="U38">
+        <v>95.814996600000001</v>
+      </c>
+      <c r="V38">
+        <v>93.135477679999994</v>
+      </c>
+      <c r="W38">
+        <v>90.355004550000004</v>
+      </c>
+      <c r="X38">
+        <v>43.841869250000002</v>
+      </c>
+      <c r="Y38">
+        <v>31.725000000000001</v>
+      </c>
+      <c r="Z38">
+        <v>22.5</v>
+      </c>
+      <c r="AA38">
+        <v>11.475</v>
+      </c>
+      <c r="AB38">
+        <v>14.11200826</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" t="s">
+        <v>49</v>
+      </c>
+      <c r="D39">
+        <v>974.75560570000005</v>
+      </c>
+      <c r="E39">
+        <v>9</v>
+      </c>
+      <c r="F39">
+        <v>10</v>
+      </c>
+      <c r="G39">
+        <v>25</v>
+      </c>
+      <c r="H39">
+        <v>18</v>
+      </c>
+      <c r="I39">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="J39">
+        <v>40.5</v>
+      </c>
+      <c r="K39">
+        <v>57.6</v>
+      </c>
+      <c r="L39">
+        <v>38.268068229999997</v>
+      </c>
+      <c r="M39">
+        <v>91.816867579999993</v>
+      </c>
+      <c r="N39">
+        <v>92.303338890000006</v>
+      </c>
+      <c r="O39">
+        <v>97.605936529999994</v>
+      </c>
+      <c r="P39">
+        <v>72.900000000000006</v>
+      </c>
+      <c r="Q39">
+        <v>78.3</v>
+      </c>
+      <c r="R39">
+        <v>67.5</v>
+      </c>
+      <c r="S39">
+        <v>67.5</v>
+      </c>
+      <c r="T39">
+        <v>46.8</v>
+      </c>
+      <c r="U39">
+        <v>30.257367349999999</v>
+      </c>
+      <c r="V39">
+        <v>30.518970079999999</v>
+      </c>
+      <c r="W39">
+        <v>29.449038510000001</v>
+      </c>
+      <c r="X39">
+        <v>14.14253847</v>
+      </c>
+      <c r="Y39">
+        <v>6.3</v>
+      </c>
+      <c r="Z39">
+        <v>14</v>
+      </c>
+      <c r="AA39">
+        <v>7.2</v>
+      </c>
+      <c r="AB39">
+        <v>10.89348006</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40">
+        <v>6392.5850419999997</v>
+      </c>
+      <c r="E40">
+        <v>174</v>
+      </c>
+      <c r="F40">
+        <v>194</v>
+      </c>
+      <c r="G40">
+        <v>165</v>
+      </c>
+      <c r="H40">
+        <v>229</v>
+      </c>
+      <c r="I40">
+        <v>240.3</v>
+      </c>
+      <c r="J40">
+        <v>223.2</v>
+      </c>
+      <c r="K40">
+        <v>182.7</v>
+      </c>
+      <c r="L40">
+        <v>208.02129400000001</v>
+      </c>
+      <c r="M40">
+        <v>399.81015760000003</v>
+      </c>
+      <c r="N40">
+        <v>519.36012019999998</v>
+      </c>
+      <c r="O40">
+        <v>439.72983779999998</v>
+      </c>
+      <c r="P40">
+        <v>351.9</v>
+      </c>
+      <c r="Q40">
+        <v>342</v>
+      </c>
+      <c r="R40">
+        <v>357.3</v>
+      </c>
+      <c r="S40">
+        <v>276.3</v>
+      </c>
+      <c r="T40">
+        <v>255.6</v>
+      </c>
+      <c r="U40">
+        <v>216.84446600000001</v>
+      </c>
+      <c r="V40">
+        <v>246.25651719999999</v>
+      </c>
+      <c r="W40">
+        <v>309.21490440000002</v>
+      </c>
+      <c r="X40">
+        <v>216.85225650000001</v>
+      </c>
+      <c r="Y40">
+        <v>213.3</v>
+      </c>
+      <c r="Z40">
+        <v>237</v>
+      </c>
+      <c r="AA40">
+        <v>189.9</v>
+      </c>
+      <c r="AB40">
+        <v>204.9954884</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41">
+        <v>522.61729279999997</v>
+      </c>
+      <c r="E41">
+        <v>46</v>
+      </c>
+      <c r="F41">
+        <v>47</v>
+      </c>
+      <c r="G41">
+        <v>55</v>
+      </c>
+      <c r="H41">
+        <v>40</v>
+      </c>
+      <c r="I41">
+        <v>29.7</v>
+      </c>
+      <c r="J41">
+        <v>19.8</v>
+      </c>
+      <c r="K41">
+        <v>14.4</v>
+      </c>
+      <c r="L41">
+        <v>5.8873951130000002</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>20.922090149999999</v>
+      </c>
+      <c r="O41">
+        <v>20.124935369999999</v>
+      </c>
+      <c r="P41">
+        <v>11.7</v>
+      </c>
+      <c r="Q41">
+        <v>18</v>
+      </c>
+      <c r="R41">
+        <v>8.1</v>
+      </c>
+      <c r="S41">
+        <v>8.1</v>
+      </c>
+      <c r="T41">
+        <v>5.4</v>
+      </c>
+      <c r="U41">
+        <v>7.5643418379999998</v>
+      </c>
+      <c r="V41">
+        <v>6.314269672</v>
+      </c>
+      <c r="W41">
+        <v>13.385926599999999</v>
+      </c>
+      <c r="X41">
+        <v>16.028210260000002</v>
+      </c>
+      <c r="Y41">
+        <v>19.8</v>
+      </c>
+      <c r="Z41">
+        <v>39</v>
+      </c>
+      <c r="AA41">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="AB41">
+        <v>31.690123809999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42">
+        <v>87418.914290000001</v>
+      </c>
+      <c r="E42">
+        <v>1158.16092</v>
+      </c>
+      <c r="F42">
+        <v>869.88505750000002</v>
+      </c>
+      <c r="G42">
+        <v>728.27586210000004</v>
+      </c>
+      <c r="H42">
+        <v>554.29885060000004</v>
+      </c>
+      <c r="I42">
+        <v>835.49425289999999</v>
+      </c>
+      <c r="J42">
+        <v>2203.0344829999999</v>
+      </c>
+      <c r="K42">
+        <v>3368.6371389999999</v>
+      </c>
+      <c r="L42">
+        <v>3635.5636690000001</v>
+      </c>
+      <c r="M42">
+        <v>3538.094834</v>
+      </c>
+      <c r="N42">
+        <v>3317.7754209999998</v>
+      </c>
+      <c r="O42">
+        <v>3561.5327090000001</v>
+      </c>
+      <c r="P42">
+        <v>4264.4597700000004</v>
+      </c>
+      <c r="Q42">
+        <v>4206.7034480000002</v>
+      </c>
+      <c r="R42">
+        <v>4716.6852310000004</v>
+      </c>
+      <c r="S42">
+        <v>5127.9724139999998</v>
+      </c>
+      <c r="T42">
+        <v>5201.1034479999998</v>
+      </c>
+      <c r="U42">
+        <v>6304.4413789999999</v>
+      </c>
+      <c r="V42">
+        <v>7168.2574709999999</v>
+      </c>
+      <c r="W42">
+        <v>7091.7885059999999</v>
+      </c>
+      <c r="X42">
+        <v>6819.8988509999999</v>
+      </c>
+      <c r="Y42">
+        <v>4040.9195399999999</v>
+      </c>
+      <c r="Z42">
+        <v>3655.5402300000001</v>
+      </c>
+      <c r="AA42">
+        <v>2948.5057470000002</v>
+      </c>
+      <c r="AB42">
+        <v>2101.885057</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43">
+        <v>2174.0700980000001</v>
+      </c>
+      <c r="E43">
+        <v>12.75</v>
+      </c>
+      <c r="F43">
+        <v>11.25</v>
+      </c>
+      <c r="G43">
+        <v>19.5</v>
+      </c>
+      <c r="H43">
+        <v>31.5</v>
+      </c>
+      <c r="I43">
+        <v>29.25</v>
+      </c>
+      <c r="J43">
+        <v>60</v>
+      </c>
+      <c r="K43">
+        <v>120.75722570000001</v>
+      </c>
+      <c r="L43">
+        <v>142.97222859999999</v>
+      </c>
+      <c r="M43">
+        <v>161.3491037</v>
+      </c>
+      <c r="N43">
+        <v>208.11595729999999</v>
+      </c>
+      <c r="O43">
+        <v>149.7845208</v>
+      </c>
+      <c r="P43">
+        <v>159</v>
+      </c>
+      <c r="Q43">
+        <v>173.47499999999999</v>
+      </c>
+      <c r="R43">
+        <v>114.66606229999999</v>
+      </c>
+      <c r="S43">
+        <v>124.2</v>
+      </c>
+      <c r="T43">
+        <v>116.25</v>
+      </c>
+      <c r="U43">
+        <v>124.95</v>
+      </c>
+      <c r="V43">
+        <v>117.6</v>
+      </c>
+      <c r="W43">
+        <v>119.7</v>
+      </c>
+      <c r="X43">
+        <v>105</v>
+      </c>
+      <c r="Y43">
+        <v>22.5</v>
+      </c>
+      <c r="Z43">
+        <v>19.5</v>
+      </c>
+      <c r="AA43">
+        <v>14.25</v>
+      </c>
+      <c r="AB43">
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44">
+        <v>979.12350319999996</v>
+      </c>
+      <c r="E44">
+        <v>12</v>
+      </c>
+      <c r="F44">
+        <v>6</v>
+      </c>
+      <c r="G44">
+        <v>7</v>
+      </c>
+      <c r="H44">
+        <v>10</v>
+      </c>
+      <c r="I44">
+        <v>21</v>
+      </c>
+      <c r="J44">
+        <v>79</v>
+      </c>
+      <c r="K44">
+        <v>72.501414260000004</v>
+      </c>
+      <c r="L44">
+        <v>68.022029439999997</v>
+      </c>
+      <c r="M44">
+        <v>72.596030200000001</v>
+      </c>
+      <c r="N44">
+        <v>68.219627220000007</v>
+      </c>
+      <c r="O44">
+        <v>67.470504849999998</v>
+      </c>
+      <c r="P44">
+        <v>85</v>
+      </c>
+      <c r="Q44">
+        <v>81</v>
+      </c>
+      <c r="R44">
+        <v>73.713897220000007</v>
+      </c>
+      <c r="S44">
+        <v>48.6</v>
+      </c>
+      <c r="T44">
+        <v>44</v>
+      </c>
+      <c r="U44">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="V44">
+        <v>36.4</v>
+      </c>
+      <c r="W44">
+        <v>25.2</v>
+      </c>
+      <c r="X44">
+        <v>26.6</v>
+      </c>
+      <c r="Y44">
+        <v>9</v>
+      </c>
+      <c r="Z44">
+        <v>11</v>
+      </c>
+      <c r="AA44">
+        <v>8</v>
+      </c>
+      <c r="AB44">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45">
+        <v>7365.523717</v>
+      </c>
+      <c r="E45">
+        <v>177</v>
+      </c>
+      <c r="F45">
+        <v>161</v>
+      </c>
+      <c r="G45">
+        <v>178</v>
+      </c>
+      <c r="H45">
+        <v>193</v>
+      </c>
+      <c r="I45">
+        <v>261</v>
+      </c>
+      <c r="J45">
+        <v>282</v>
+      </c>
+      <c r="K45">
+        <v>222.21212679999999</v>
+      </c>
+      <c r="L45">
+        <v>248.57432979999999</v>
+      </c>
+      <c r="M45">
+        <v>350.58570680000003</v>
+      </c>
+      <c r="N45">
+        <v>427.75550040000002</v>
+      </c>
+      <c r="O45">
+        <v>421.91555699999998</v>
+      </c>
+      <c r="P45">
+        <v>442</v>
+      </c>
+      <c r="Q45">
+        <v>417.6</v>
+      </c>
+      <c r="R45">
+        <v>387.6804965</v>
+      </c>
+      <c r="S45">
+        <v>316.8</v>
+      </c>
+      <c r="T45">
+        <v>312</v>
+      </c>
+      <c r="U45">
+        <v>372.4</v>
+      </c>
+      <c r="V45">
+        <v>401.8</v>
+      </c>
+      <c r="W45">
+        <v>456.4</v>
+      </c>
+      <c r="X45">
+        <v>436.8</v>
+      </c>
+      <c r="Y45">
+        <v>262</v>
+      </c>
+      <c r="Z45">
+        <v>221</v>
+      </c>
+      <c r="AA45">
+        <v>222</v>
+      </c>
+      <c r="AB45">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46">
+        <v>616.3282117</v>
+      </c>
+      <c r="E46">
+        <v>42</v>
+      </c>
+      <c r="F46">
+        <v>44</v>
+      </c>
+      <c r="G46">
+        <v>35</v>
+      </c>
+      <c r="H46">
+        <v>27</v>
+      </c>
+      <c r="I46">
+        <v>34</v>
+      </c>
+      <c r="J46">
+        <v>29</v>
+      </c>
+      <c r="K46">
+        <v>26.364150639999998</v>
+      </c>
+      <c r="L46">
+        <v>21.834231670000001</v>
+      </c>
+      <c r="M46">
+        <v>19.476983709999999</v>
+      </c>
+      <c r="N46">
+        <v>33.187926750000003</v>
+      </c>
+      <c r="O46">
+        <v>13.49410097</v>
+      </c>
+      <c r="P46">
+        <v>23</v>
+      </c>
+      <c r="Q46">
+        <v>18</v>
+      </c>
+      <c r="R46">
+        <v>15.470817930000001</v>
+      </c>
+      <c r="S46">
+        <v>11.7</v>
+      </c>
+      <c r="T46">
+        <v>12</v>
+      </c>
+      <c r="U46">
+        <v>22.4</v>
+      </c>
+      <c r="V46">
+        <v>18.2</v>
+      </c>
+      <c r="W46">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="X46">
+        <v>35</v>
+      </c>
+      <c r="Y46">
+        <v>19</v>
+      </c>
+      <c r="Z46">
+        <v>23</v>
+      </c>
+      <c r="AA46">
+        <v>24</v>
+      </c>
+      <c r="AB46">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47">
+        <v>87121.532510000005</v>
+      </c>
+      <c r="E47">
+        <v>641.28735630000006</v>
+      </c>
+      <c r="F47">
+        <v>444.04597699999999</v>
+      </c>
+      <c r="G47">
+        <v>440</v>
+      </c>
+      <c r="H47">
+        <v>728.27586210000004</v>
+      </c>
+      <c r="I47">
+        <v>1795.4022990000001</v>
+      </c>
+      <c r="J47">
+        <v>5120.6896550000001</v>
+      </c>
+      <c r="K47">
+        <v>5919.0620689999996</v>
+      </c>
+      <c r="L47">
+        <v>6003.0486279999996</v>
+      </c>
+      <c r="M47">
+        <v>5907.9997700000004</v>
+      </c>
+      <c r="N47">
+        <v>5906.0717679999998</v>
+      </c>
+      <c r="O47">
+        <v>5087.340099</v>
+      </c>
+      <c r="P47">
+        <v>4470.7342179999996</v>
+      </c>
+      <c r="Q47">
+        <v>4499.7821130000002</v>
+      </c>
+      <c r="R47">
+        <v>4490.7310340000004</v>
+      </c>
+      <c r="S47">
+        <v>4836.9729639999996</v>
+      </c>
+      <c r="T47">
+        <v>5032.7640689999998</v>
+      </c>
+      <c r="U47">
+        <v>4240.7014920000001</v>
+      </c>
+      <c r="V47">
+        <v>4469.5991489999997</v>
+      </c>
+      <c r="W47">
+        <v>5213.2112690000004</v>
+      </c>
+      <c r="X47">
+        <v>3954.8242150000001</v>
+      </c>
+      <c r="Y47">
+        <v>2734.0689659999998</v>
+      </c>
+      <c r="Z47">
+        <v>2351.724138</v>
+      </c>
+      <c r="AA47">
+        <v>1747.862069</v>
+      </c>
+      <c r="AB47">
+        <v>1085.333333</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" t="s">
+        <v>48</v>
+      </c>
+      <c r="D48">
+        <v>2291.5333300000002</v>
+      </c>
+      <c r="E48">
+        <v>21</v>
+      </c>
+      <c r="F48">
+        <v>24.75</v>
+      </c>
+      <c r="G48">
+        <v>18</v>
+      </c>
+      <c r="H48">
+        <v>23.25</v>
+      </c>
+      <c r="I48">
+        <v>31.5</v>
+      </c>
+      <c r="J48">
+        <v>54</v>
+      </c>
+      <c r="K48">
+        <v>99.9</v>
+      </c>
+      <c r="L48">
+        <v>160.15210870000001</v>
+      </c>
+      <c r="M48">
+        <v>225.56874490000001</v>
+      </c>
+      <c r="N48">
+        <v>228.7069334</v>
+      </c>
+      <c r="O48">
+        <v>177.25546080000001</v>
+      </c>
+      <c r="P48">
+        <v>177.0187913</v>
+      </c>
+      <c r="Q48">
+        <v>188.0206431</v>
+      </c>
+      <c r="R48">
+        <v>151.875</v>
+      </c>
+      <c r="S48">
+        <v>141.9728858</v>
+      </c>
+      <c r="T48">
+        <v>119.43014460000001</v>
+      </c>
+      <c r="U48">
+        <v>95.628474449999999</v>
+      </c>
+      <c r="V48">
+        <v>89.553859579999994</v>
+      </c>
+      <c r="W48">
+        <v>94.365984749999996</v>
+      </c>
+      <c r="X48">
+        <v>59.33429829</v>
+      </c>
+      <c r="Y48">
+        <v>35.25</v>
+      </c>
+      <c r="Z48">
+        <v>25.5</v>
+      </c>
+      <c r="AA48">
+        <v>27.75</v>
+      </c>
+      <c r="AB48">
+        <v>21.75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" t="s">
+        <v>52</v>
+      </c>
+      <c r="C49" t="s">
+        <v>49</v>
+      </c>
+      <c r="D49">
+        <v>977.09918019999998</v>
+      </c>
+      <c r="E49">
+        <v>10</v>
+      </c>
+      <c r="F49">
+        <v>11</v>
+      </c>
+      <c r="G49">
+        <v>6</v>
+      </c>
+      <c r="H49">
+        <v>7</v>
+      </c>
+      <c r="I49">
+        <v>31</v>
+      </c>
+      <c r="J49">
+        <v>39.6</v>
+      </c>
+      <c r="K49">
+        <v>56.7</v>
+      </c>
+      <c r="L49">
+        <v>44.17989206</v>
+      </c>
+      <c r="M49">
+        <v>92.2781229</v>
+      </c>
+      <c r="N49">
+        <v>80.855986569999999</v>
+      </c>
+      <c r="O49">
+        <v>109.6218169</v>
+      </c>
+      <c r="P49">
+        <v>79.959508459999995</v>
+      </c>
+      <c r="Q49">
+        <v>82.625800720000001</v>
+      </c>
+      <c r="R49">
+        <v>72.900000000000006</v>
+      </c>
+      <c r="S49">
+        <v>64.000475530000003</v>
+      </c>
+      <c r="T49">
+        <v>50.956861709999998</v>
+      </c>
+      <c r="U49">
+        <v>28.688542340000001</v>
+      </c>
+      <c r="V49">
+        <v>30.26020827</v>
+      </c>
+      <c r="W49">
+        <v>28.221602910000001</v>
+      </c>
+      <c r="X49">
+        <v>22.250361860000002</v>
+      </c>
+      <c r="Y49">
+        <v>2</v>
+      </c>
+      <c r="Z49">
+        <v>12</v>
+      </c>
+      <c r="AA49">
+        <v>5</v>
+      </c>
+      <c r="AB49">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" t="s">
+        <v>50</v>
+      </c>
+      <c r="D50">
+        <v>6966.0833510000002</v>
+      </c>
+      <c r="E50">
+        <v>180</v>
+      </c>
+      <c r="F50">
+        <v>185</v>
+      </c>
+      <c r="G50">
+        <v>174</v>
+      </c>
+      <c r="H50">
+        <v>241</v>
+      </c>
+      <c r="I50">
+        <v>274</v>
+      </c>
+      <c r="J50">
+        <v>225.9</v>
+      </c>
+      <c r="K50">
+        <v>203.4</v>
+      </c>
+      <c r="L50">
+        <v>254.5603304</v>
+      </c>
+      <c r="M50">
+        <v>444.3020732</v>
+      </c>
+      <c r="N50">
+        <v>519.7884851</v>
+      </c>
+      <c r="O50">
+        <v>485.75539049999998</v>
+      </c>
+      <c r="P50">
+        <v>414.2480559</v>
+      </c>
+      <c r="Q50">
+        <v>399.04506029999999</v>
+      </c>
+      <c r="R50">
+        <v>395.1</v>
+      </c>
+      <c r="S50">
+        <v>314.59388669999998</v>
+      </c>
+      <c r="T50">
+        <v>289.36217900000003</v>
+      </c>
+      <c r="U50">
+        <v>237.4773783</v>
+      </c>
+      <c r="V50">
+        <v>226.54264029999999</v>
+      </c>
+      <c r="W50">
+        <v>290.44733000000002</v>
+      </c>
+      <c r="X50">
+        <v>306.56054110000002</v>
+      </c>
+      <c r="Y50">
+        <v>238</v>
+      </c>
+      <c r="Z50">
+        <v>245</v>
+      </c>
+      <c r="AA50">
+        <v>201</v>
+      </c>
+      <c r="AB50">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51">
+        <v>608.58696399999997</v>
+      </c>
+      <c r="E51">
+        <v>41</v>
+      </c>
+      <c r="F51">
+        <v>47</v>
+      </c>
+      <c r="G51">
+        <v>48</v>
+      </c>
+      <c r="H51">
+        <v>44</v>
+      </c>
+      <c r="I51">
+        <v>34</v>
+      </c>
+      <c r="J51">
+        <v>19.8</v>
+      </c>
+      <c r="K51">
+        <v>14.4</v>
+      </c>
+      <c r="L51">
+        <v>7.363315343</v>
+      </c>
+      <c r="M51">
+        <v>26.20242996</v>
+      </c>
+      <c r="N51">
+        <v>23.101710449999999</v>
+      </c>
+      <c r="O51">
+        <v>29.165437529999998</v>
+      </c>
+      <c r="P51">
+        <v>16.377248720000001</v>
+      </c>
+      <c r="Q51">
+        <v>25.35109795</v>
+      </c>
+      <c r="R51">
+        <v>13.5</v>
+      </c>
+      <c r="S51">
+        <v>13.52122722</v>
+      </c>
+      <c r="T51">
+        <v>5.4596637550000002</v>
+      </c>
+      <c r="U51">
+        <v>9.5628474469999993</v>
+      </c>
+      <c r="V51">
+        <v>7.3605912</v>
+      </c>
+      <c r="W51">
+        <v>12.934901330000001</v>
+      </c>
+      <c r="X51">
+        <v>23.486493070000002</v>
+      </c>
+      <c r="Y51">
+        <v>27</v>
+      </c>
+      <c r="Z51">
+        <v>43</v>
+      </c>
+      <c r="AA51">
+        <v>44</v>
+      </c>
+      <c r="AB51">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" t="s">
+        <v>47</v>
+      </c>
+      <c r="D52">
+        <v>86229.891610000006</v>
+      </c>
+      <c r="E52">
+        <v>1124.7816089999999</v>
+      </c>
+      <c r="F52">
+        <v>815.26436779999995</v>
+      </c>
+      <c r="G52">
+        <v>651.90804600000001</v>
+      </c>
+      <c r="H52">
+        <v>594.25287360000004</v>
+      </c>
+      <c r="I52">
+        <v>902.25287360000004</v>
+      </c>
+      <c r="J52">
+        <v>2251.5862069999998</v>
+      </c>
+      <c r="K52">
+        <v>3399.609598</v>
+      </c>
+      <c r="L52">
+        <v>3592.0966250000001</v>
+      </c>
+      <c r="M52">
+        <v>3484.2255949999999</v>
+      </c>
+      <c r="N52">
+        <v>3234.3194210000001</v>
+      </c>
+      <c r="O52">
+        <v>3365.6459620000001</v>
+      </c>
+      <c r="P52">
+        <v>3640.0137930000001</v>
+      </c>
+      <c r="Q52">
+        <v>4247.2137929999999</v>
+      </c>
+      <c r="R52">
+        <v>4679.1724139999997</v>
+      </c>
+      <c r="S52">
+        <v>5370.1241380000001</v>
+      </c>
+      <c r="T52">
+        <v>5339.6275859999996</v>
+      </c>
+      <c r="U52">
+        <v>6070.7831859999997</v>
+      </c>
+      <c r="V52">
+        <v>7076.5540979999996</v>
+      </c>
+      <c r="W52">
+        <v>7043.7302669999999</v>
+      </c>
+      <c r="X52">
+        <v>6607.9705400000003</v>
+      </c>
+      <c r="Y52">
+        <v>4171.4022990000003</v>
+      </c>
+      <c r="Z52">
+        <v>3611.0344829999999</v>
+      </c>
+      <c r="AA52">
+        <v>2892.3678159999999</v>
+      </c>
+      <c r="AB52">
+        <v>2063.9540229999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>36</v>
+      </c>
+      <c r="B53" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" t="s">
+        <v>48</v>
+      </c>
+      <c r="D53">
+        <v>2158.5990190000002</v>
+      </c>
+      <c r="E53">
+        <v>13.5</v>
+      </c>
+      <c r="F53">
+        <v>18.75</v>
+      </c>
+      <c r="G53">
+        <v>14.25</v>
+      </c>
+      <c r="H53">
+        <v>24.375</v>
+      </c>
+      <c r="I53">
+        <v>34.875</v>
+      </c>
+      <c r="J53">
+        <v>64.5</v>
+      </c>
+      <c r="K53">
+        <v>133.78489049999999</v>
+      </c>
+      <c r="L53">
+        <v>161.7789569</v>
+      </c>
+      <c r="M53">
+        <v>182.8502537</v>
+      </c>
+      <c r="N53">
+        <v>190.96640840000001</v>
+      </c>
+      <c r="O53">
+        <v>153.166031</v>
+      </c>
+      <c r="P53">
+        <v>149.85</v>
+      </c>
+      <c r="Q53">
+        <v>143.4375</v>
+      </c>
+      <c r="R53">
+        <v>149.85</v>
+      </c>
+      <c r="S53">
+        <v>115.08750000000001</v>
+      </c>
+      <c r="T53">
+        <v>99.9</v>
+      </c>
+      <c r="U53">
+        <v>118.8193598</v>
+      </c>
+      <c r="V53">
+        <v>117.30216919999999</v>
+      </c>
+      <c r="W53">
+        <v>111.88365949999999</v>
+      </c>
+      <c r="X53">
+        <v>83.547290180000005</v>
+      </c>
+      <c r="Y53">
+        <v>24</v>
+      </c>
+      <c r="Z53">
+        <v>16.5</v>
+      </c>
+      <c r="AA53">
+        <v>23.25</v>
+      </c>
+      <c r="AB53">
+        <v>12.375</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>36</v>
+      </c>
+      <c r="B54" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" t="s">
+        <v>49</v>
+      </c>
+      <c r="D54">
+        <v>795.01847399999997</v>
+      </c>
+      <c r="E54">
+        <v>4.5</v>
+      </c>
+      <c r="F54">
+        <v>2.5</v>
+      </c>
+      <c r="G54">
+        <v>6</v>
+      </c>
+      <c r="H54">
+        <v>6</v>
+      </c>
+      <c r="I54">
+        <v>7.5</v>
+      </c>
+      <c r="J54">
+        <v>52.5</v>
+      </c>
+      <c r="K54">
+        <v>55.067131699999997</v>
+      </c>
+      <c r="L54">
+        <v>60.694399480000001</v>
+      </c>
+      <c r="M54">
+        <v>58.56922187</v>
+      </c>
+      <c r="N54">
+        <v>70.809131719999996</v>
+      </c>
+      <c r="O54">
+        <v>55.896798680000003</v>
+      </c>
+      <c r="P54">
+        <v>64.8</v>
+      </c>
+      <c r="Q54">
+        <v>61.65</v>
+      </c>
+      <c r="R54">
+        <v>66.150000000000006</v>
+      </c>
+      <c r="S54">
+        <v>46.8</v>
+      </c>
+      <c r="T54">
+        <v>36</v>
+      </c>
+      <c r="U54">
+        <v>31.360741149999999</v>
+      </c>
+      <c r="V54">
+        <v>35.297150770000002</v>
+      </c>
+      <c r="W54">
+        <v>26.28960305</v>
+      </c>
+      <c r="X54">
+        <v>18.134295529999999</v>
+      </c>
+      <c r="Y54">
+        <v>6.5</v>
+      </c>
+      <c r="Z54">
+        <v>7</v>
+      </c>
+      <c r="AA54">
+        <v>3</v>
+      </c>
+      <c r="AB54">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" t="s">
+        <v>46</v>
+      </c>
+      <c r="C55" t="s">
+        <v>50</v>
+      </c>
+      <c r="D55">
+        <v>7231.5012740000002</v>
+      </c>
+      <c r="E55">
+        <v>178.5</v>
+      </c>
+      <c r="F55">
+        <v>173.5</v>
+      </c>
+      <c r="G55">
+        <v>174</v>
+      </c>
+      <c r="H55">
+        <v>185</v>
+      </c>
+      <c r="I55">
+        <v>257</v>
+      </c>
+      <c r="J55">
+        <v>277</v>
+      </c>
+      <c r="K55">
+        <v>242.38951130000001</v>
+      </c>
+      <c r="L55">
+        <v>252.38390580000001</v>
+      </c>
+      <c r="M55">
+        <v>381.41420099999999</v>
+      </c>
+      <c r="N55">
+        <v>443.76955839999999</v>
+      </c>
+      <c r="O55">
+        <v>441.01253759999997</v>
+      </c>
+      <c r="P55">
+        <v>436.95</v>
+      </c>
+      <c r="Q55">
+        <v>410.85</v>
+      </c>
+      <c r="R55">
+        <v>381.6</v>
+      </c>
+      <c r="S55">
+        <v>330.75</v>
+      </c>
+      <c r="T55">
+        <v>268.64999999999998</v>
+      </c>
+      <c r="U55">
+        <v>291.43861170000002</v>
+      </c>
+      <c r="V55">
+        <v>365.75151060000002</v>
+      </c>
+      <c r="W55">
+        <v>414.51978759999997</v>
+      </c>
+      <c r="X55">
+        <v>408.02164950000002</v>
+      </c>
+      <c r="Y55">
+        <v>272.5</v>
+      </c>
+      <c r="Z55">
+        <v>228</v>
+      </c>
+      <c r="AA55">
+        <v>221.5</v>
+      </c>
+      <c r="AB55">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" t="s">
+        <v>51</v>
+      </c>
+      <c r="D56">
+        <v>548.66083449999996</v>
+      </c>
+      <c r="E56">
+        <v>36</v>
+      </c>
+      <c r="F56">
+        <v>37</v>
+      </c>
+      <c r="G56">
+        <v>28</v>
+      </c>
+      <c r="H56">
+        <v>29</v>
+      </c>
+      <c r="I56">
+        <v>33.5</v>
+      </c>
+      <c r="J56">
+        <v>23</v>
+      </c>
+      <c r="K56">
+        <v>21.179666040000001</v>
+      </c>
+      <c r="L56">
+        <v>23.579119219999999</v>
+      </c>
+      <c r="M56">
+        <v>22.380109170000001</v>
+      </c>
+      <c r="N56">
+        <v>33.464589650000001</v>
+      </c>
+      <c r="O56">
+        <v>14.084232739999999</v>
+      </c>
+      <c r="P56">
+        <v>17.55</v>
+      </c>
+      <c r="Q56">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="R56">
+        <v>15.75</v>
+      </c>
+      <c r="S56">
+        <v>9.9</v>
+      </c>
+      <c r="T56">
+        <v>11.25</v>
+      </c>
+      <c r="U56">
+        <v>14.058263269999999</v>
+      </c>
+      <c r="V56">
+        <v>16.43143225</v>
+      </c>
+      <c r="W56">
+        <v>24.455444700000001</v>
+      </c>
+      <c r="X56">
+        <v>33.677977419999998</v>
+      </c>
+      <c r="Y56">
+        <v>16.5</v>
+      </c>
+      <c r="Z56">
+        <v>14.5</v>
+      </c>
+      <c r="AA56">
+        <v>18</v>
+      </c>
+      <c r="AB56">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>36</v>
+      </c>
+      <c r="B57" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" t="s">
+        <v>47</v>
+      </c>
+      <c r="D57">
+        <v>88265.999290000007</v>
+      </c>
+      <c r="E57">
+        <v>629.14942529999996</v>
+      </c>
+      <c r="F57">
+        <v>469.83908050000002</v>
+      </c>
+      <c r="G57">
+        <v>480.96551720000002</v>
+      </c>
+      <c r="H57">
+        <v>855.21839079999995</v>
+      </c>
+      <c r="I57">
+        <v>1853.0574710000001</v>
+      </c>
+      <c r="J57">
+        <v>5172.5793100000001</v>
+      </c>
+      <c r="K57">
+        <v>5766.1241380000001</v>
+      </c>
+      <c r="L57">
+        <v>6444.6063029999996</v>
+      </c>
+      <c r="M57">
+        <v>6485.2647749999996</v>
+      </c>
+      <c r="N57">
+        <v>6147.9202880000003</v>
+      </c>
+      <c r="O57">
+        <v>5184.1216199999999</v>
+      </c>
+      <c r="P57">
+        <v>4468.9331179999999</v>
+      </c>
+      <c r="Q57">
+        <v>4193.0482760000004</v>
+      </c>
+      <c r="R57">
+        <v>4385.5862070000003</v>
+      </c>
+      <c r="S57">
+        <v>4592.2344830000002</v>
+      </c>
+      <c r="T57">
+        <v>4727.8758619999999</v>
+      </c>
+      <c r="U57">
+        <v>4456.5507369999996</v>
+      </c>
+      <c r="V57">
+        <v>4731.5138129999996</v>
+      </c>
+      <c r="W57">
+        <v>4996.0863390000004</v>
+      </c>
+      <c r="X57">
+        <v>4412.5425290000003</v>
+      </c>
+      <c r="Y57">
+        <v>2651.1264369999999</v>
+      </c>
+      <c r="Z57">
+        <v>2365.885057</v>
+      </c>
+      <c r="AA57">
+        <v>1728.137931</v>
+      </c>
+      <c r="AB57">
+        <v>1067.6321840000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" t="s">
+        <v>52</v>
+      </c>
+      <c r="C58" t="s">
+        <v>48</v>
+      </c>
+      <c r="D58">
+        <v>2257.995488</v>
+      </c>
+      <c r="E58">
+        <v>23.625</v>
+      </c>
+      <c r="F58">
+        <v>19.5</v>
+      </c>
+      <c r="G58">
+        <v>18</v>
+      </c>
+      <c r="H58">
+        <v>17.625</v>
+      </c>
+      <c r="I58">
+        <v>33</v>
+      </c>
+      <c r="J58">
+        <v>54.674999999999997</v>
+      </c>
+      <c r="K58">
+        <v>100.2375</v>
+      </c>
+      <c r="L58">
+        <v>168.6107279</v>
+      </c>
+      <c r="M58">
+        <v>233.9152579</v>
+      </c>
+      <c r="N58">
+        <v>213.26784810000001</v>
+      </c>
+      <c r="O58">
+        <v>191.28641239999999</v>
+      </c>
+      <c r="P58">
+        <v>173.83492029999999</v>
+      </c>
+      <c r="Q58">
+        <v>173.8125</v>
+      </c>
+      <c r="R58">
+        <v>137.69999999999999</v>
+      </c>
+      <c r="S58">
+        <v>146.13749999999999</v>
+      </c>
+      <c r="T58">
+        <v>110.3625</v>
+      </c>
+      <c r="U58">
+        <v>113.0669656</v>
+      </c>
+      <c r="V58">
+        <v>101.2298771</v>
+      </c>
+      <c r="W58">
+        <v>85.533479099999994</v>
+      </c>
+      <c r="X58">
+        <v>64.575000000000003</v>
+      </c>
+      <c r="Y58">
+        <v>24</v>
+      </c>
+      <c r="Z58">
+        <v>23.625</v>
+      </c>
+      <c r="AA58">
+        <v>14.25</v>
+      </c>
+      <c r="AB58">
+        <v>16.125</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B59" t="s">
+        <v>52</v>
+      </c>
+      <c r="C59" t="s">
+        <v>49</v>
+      </c>
+      <c r="D59">
+        <v>831.35081920000005</v>
+      </c>
+      <c r="E59">
+        <v>5.5</v>
+      </c>
+      <c r="F59">
+        <v>5</v>
+      </c>
+      <c r="G59">
+        <v>3.5</v>
+      </c>
+      <c r="H59">
+        <v>7.5</v>
+      </c>
+      <c r="I59">
+        <v>10</v>
+      </c>
+      <c r="J59">
+        <v>28.8</v>
+      </c>
+      <c r="K59">
+        <v>45.45</v>
+      </c>
+      <c r="L59">
+        <v>48.393269789999998</v>
+      </c>
+      <c r="M59">
+        <v>79.697485589999999</v>
+      </c>
+      <c r="N59">
+        <v>85.855150829999999</v>
+      </c>
+      <c r="O59">
+        <v>103.28412350000001</v>
+      </c>
+      <c r="P59">
+        <v>62.763425380000001</v>
+      </c>
+      <c r="Q59">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="R59">
+        <v>57.6</v>
+      </c>
+      <c r="S59">
+        <v>50.4</v>
+      </c>
+      <c r="T59">
+        <v>41.85</v>
+      </c>
+      <c r="U59">
+        <v>33.54973545</v>
+      </c>
+      <c r="V59">
+        <v>27.788593729999999</v>
+      </c>
+      <c r="W59">
+        <v>24.719035000000002</v>
+      </c>
+      <c r="X59">
+        <v>16.8</v>
+      </c>
+      <c r="Y59">
+        <v>5.5</v>
+      </c>
+      <c r="Z59">
+        <v>13</v>
+      </c>
+      <c r="AA59">
+        <v>1.5</v>
+      </c>
+      <c r="AB59">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" t="s">
+        <v>52</v>
+      </c>
+      <c r="C60" t="s">
+        <v>50</v>
+      </c>
+      <c r="D60">
+        <v>7159.9877930000002</v>
+      </c>
+      <c r="E60">
+        <v>202</v>
+      </c>
+      <c r="F60">
+        <v>181.5</v>
+      </c>
+      <c r="G60">
+        <v>160.5</v>
+      </c>
+      <c r="H60">
+        <v>249</v>
+      </c>
+      <c r="I60">
+        <v>278</v>
+      </c>
+      <c r="J60">
+        <v>234.45</v>
+      </c>
+      <c r="K60">
+        <v>197.55</v>
+      </c>
+      <c r="L60">
+        <v>290.97219180000002</v>
+      </c>
+      <c r="M60">
+        <v>492.61831640000003</v>
+      </c>
+      <c r="N60">
+        <v>527.91784229999996</v>
+      </c>
+      <c r="O60">
+        <v>500.08486310000001</v>
+      </c>
+      <c r="P60">
+        <v>416.11656829999998</v>
+      </c>
+      <c r="Q60">
+        <v>385.65</v>
+      </c>
+      <c r="R60">
+        <v>385.2</v>
+      </c>
+      <c r="S60">
+        <v>305.55</v>
+      </c>
+      <c r="T60">
+        <v>291.60000000000002</v>
+      </c>
+      <c r="U60">
+        <v>269.70501610000002</v>
+      </c>
+      <c r="V60">
+        <v>247.00972200000001</v>
+      </c>
+      <c r="W60">
+        <v>288.76327259999999</v>
+      </c>
+      <c r="X60">
+        <v>338.8</v>
+      </c>
+      <c r="Y60">
+        <v>238</v>
+      </c>
+      <c r="Z60">
+        <v>236</v>
+      </c>
+      <c r="AA60">
+        <v>222</v>
+      </c>
+      <c r="AB60">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" t="s">
+        <v>52</v>
+      </c>
+      <c r="C61" t="s">
+        <v>51</v>
+      </c>
+      <c r="D61">
+        <v>524.9851582</v>
+      </c>
+      <c r="E61">
+        <v>19</v>
+      </c>
+      <c r="F61">
+        <v>40.5</v>
+      </c>
+      <c r="G61">
+        <v>53</v>
+      </c>
+      <c r="H61">
+        <v>41.5</v>
+      </c>
+      <c r="I61">
+        <v>15</v>
+      </c>
+      <c r="J61">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="K61">
+        <v>10.35</v>
+      </c>
+      <c r="L61">
+        <v>10.4137416</v>
+      </c>
+      <c r="M61">
+        <v>27.611727290000001</v>
+      </c>
+      <c r="N61">
+        <v>23.138267599999999</v>
+      </c>
+      <c r="O61">
+        <v>26.87495049</v>
+      </c>
+      <c r="P61">
+        <v>14.826006</v>
+      </c>
+      <c r="Q61">
+        <v>23.4</v>
+      </c>
+      <c r="R61">
+        <v>13.05</v>
+      </c>
+      <c r="S61">
+        <v>11.25</v>
+      </c>
+      <c r="T61">
+        <v>6.75</v>
+      </c>
+      <c r="U61">
+        <v>10.02134955</v>
+      </c>
+      <c r="V61">
+        <v>7.9395982089999997</v>
+      </c>
+      <c r="W61">
+        <v>12.359517500000001</v>
+      </c>
+      <c r="X61">
+        <v>26.6</v>
+      </c>
+      <c r="Y61">
+        <v>25.5</v>
+      </c>
+      <c r="Z61">
+        <v>37</v>
+      </c>
+      <c r="AA61">
+        <v>17.5</v>
+      </c>
+      <c r="AB61">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" t="s">
+        <v>46</v>
+      </c>
+      <c r="C62" t="s">
+        <v>47</v>
+      </c>
+      <c r="D62">
+        <v>81657.056630000006</v>
+      </c>
+      <c r="E62">
+        <v>944.73563220000005</v>
+      </c>
+      <c r="F62">
+        <v>699.4482759</v>
+      </c>
+      <c r="G62">
+        <v>545.19540229999996</v>
+      </c>
+      <c r="H62">
+        <v>567.4482759</v>
+      </c>
+      <c r="I62">
+        <v>917.4252874</v>
+      </c>
+      <c r="J62">
+        <v>2466.5287360000002</v>
+      </c>
+      <c r="K62">
+        <v>3785.5317249999998</v>
+      </c>
+      <c r="L62">
+        <v>3779.808814</v>
+      </c>
+      <c r="M62">
+        <v>3454.7869540000002</v>
+      </c>
+      <c r="N62">
+        <v>3256.7136529999998</v>
+      </c>
+      <c r="O62">
+        <v>3409.3317179999999</v>
+      </c>
+      <c r="P62">
+        <v>3438.3724139999999</v>
+      </c>
+      <c r="Q62">
+        <v>4028.7310339999999</v>
+      </c>
+      <c r="R62">
+        <v>4491.6413789999997</v>
+      </c>
+      <c r="S62">
+        <v>5219.9172410000001</v>
+      </c>
+      <c r="T62">
+        <v>5347.8206899999996</v>
+      </c>
+      <c r="U62">
+        <v>5612.9410529999996</v>
+      </c>
+      <c r="V62">
+        <v>6570.0200210000003</v>
+      </c>
+      <c r="W62">
+        <v>6314.8229140000003</v>
+      </c>
+      <c r="X62">
+        <v>5819.9963280000002</v>
+      </c>
+      <c r="Y62">
+        <v>3712.183908</v>
+      </c>
+      <c r="Z62">
+        <v>3093.1494250000001</v>
+      </c>
+      <c r="AA62">
+        <v>2424.0459770000002</v>
+      </c>
+      <c r="AB62">
+        <v>1756.4597699999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" t="s">
+        <v>46</v>
+      </c>
+      <c r="C63" t="s">
+        <v>48</v>
+      </c>
+      <c r="D63">
+        <v>1904.294615</v>
+      </c>
+      <c r="E63">
+        <v>16.875</v>
+      </c>
+      <c r="F63">
+        <v>18.375</v>
+      </c>
+      <c r="G63">
+        <v>13.875</v>
+      </c>
+      <c r="H63">
+        <v>19.875</v>
+      </c>
+      <c r="I63">
+        <v>25.875</v>
+      </c>
+      <c r="J63">
+        <v>57</v>
+      </c>
+      <c r="K63">
+        <v>109.77032629999999</v>
+      </c>
+      <c r="L63">
+        <v>150.22135399999999</v>
+      </c>
+      <c r="M63">
+        <v>167.19367879999999</v>
+      </c>
+      <c r="N63">
+        <v>152.24263099999999</v>
+      </c>
+      <c r="O63">
+        <v>128.3762328</v>
+      </c>
+      <c r="P63">
+        <v>139.72499999999999</v>
+      </c>
+      <c r="Q63">
+        <v>131.28749999999999</v>
+      </c>
+      <c r="R63">
+        <v>124.2</v>
+      </c>
+      <c r="S63">
+        <v>118.125</v>
+      </c>
+      <c r="T63">
+        <v>96.862499999999997</v>
+      </c>
+      <c r="U63">
+        <v>94.866371330000007</v>
+      </c>
+      <c r="V63">
+        <v>95.143695149999999</v>
+      </c>
+      <c r="W63">
+        <v>97.217741849999996</v>
+      </c>
+      <c r="X63">
+        <v>57.562584469999997</v>
+      </c>
+      <c r="Y63">
+        <v>30</v>
+      </c>
+      <c r="Z63">
+        <v>25.5</v>
+      </c>
+      <c r="AA63">
+        <v>20.625</v>
+      </c>
+      <c r="AB63">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64" t="s">
+        <v>49</v>
+      </c>
+      <c r="D64">
+        <v>801.23033699999996</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>2</v>
+      </c>
+      <c r="G64">
+        <v>5.5</v>
+      </c>
+      <c r="H64">
+        <v>6</v>
+      </c>
+      <c r="I64">
+        <v>7</v>
+      </c>
+      <c r="J64">
+        <v>53.5</v>
+      </c>
+      <c r="K64">
+        <v>53.221976349999998</v>
+      </c>
+      <c r="L64">
+        <v>55.917635939999997</v>
+      </c>
+      <c r="M64">
+        <v>62.697629569999997</v>
+      </c>
+      <c r="N64">
+        <v>73.860286329999994</v>
+      </c>
+      <c r="O64">
+        <v>57.531570989999999</v>
+      </c>
+      <c r="P64">
+        <v>71.099999999999994</v>
+      </c>
+      <c r="Q64">
+        <v>61.2</v>
+      </c>
+      <c r="R64">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="S64">
+        <v>53.1</v>
+      </c>
+      <c r="T64">
+        <v>43.65</v>
+      </c>
+      <c r="U64">
+        <v>27.538085649999999</v>
+      </c>
+      <c r="V64">
+        <v>34.845187340000003</v>
+      </c>
+      <c r="W64">
+        <v>27.980436709999999</v>
+      </c>
+      <c r="X64">
+        <v>19.187528159999999</v>
+      </c>
+      <c r="Y64">
+        <v>4</v>
+      </c>
+      <c r="Z64">
+        <v>7</v>
+      </c>
+      <c r="AA64">
+        <v>2</v>
+      </c>
+      <c r="AB64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" t="s">
+        <v>50</v>
+      </c>
+      <c r="D65">
+        <v>7223.711096</v>
+      </c>
+      <c r="E65">
+        <v>181</v>
+      </c>
+      <c r="F65">
+        <v>204</v>
+      </c>
+      <c r="G65">
+        <v>189</v>
+      </c>
+      <c r="H65">
+        <v>191</v>
+      </c>
+      <c r="I65">
+        <v>272</v>
+      </c>
+      <c r="J65">
+        <v>276.5</v>
+      </c>
+      <c r="K65">
+        <v>237.66365300000001</v>
+      </c>
+      <c r="L65">
+        <v>251.6293617</v>
+      </c>
+      <c r="M65">
+        <v>410.02259340000001</v>
+      </c>
+      <c r="N65">
+        <v>471.80142089999998</v>
+      </c>
+      <c r="O65">
+        <v>451.69415240000001</v>
+      </c>
+      <c r="P65">
+        <v>427.5</v>
+      </c>
+      <c r="Q65">
+        <v>405</v>
+      </c>
+      <c r="R65">
+        <v>380.7</v>
+      </c>
+      <c r="S65">
+        <v>327.14999999999998</v>
+      </c>
+      <c r="T65">
+        <v>273.14999999999998</v>
+      </c>
+      <c r="U65">
+        <v>253.4437374</v>
+      </c>
+      <c r="V65">
+        <v>332.66264790000002</v>
+      </c>
+      <c r="W65">
+        <v>401.43361240000002</v>
+      </c>
+      <c r="X65">
+        <v>369.359917</v>
+      </c>
+      <c r="Y65">
+        <v>286</v>
+      </c>
+      <c r="Z65">
+        <v>223.5</v>
+      </c>
+      <c r="AA65">
+        <v>212</v>
+      </c>
+      <c r="AB65">
+        <v>195.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" t="s">
+        <v>46</v>
+      </c>
+      <c r="C66" t="s">
+        <v>51</v>
+      </c>
+      <c r="D66">
+        <v>525.11976909999998</v>
+      </c>
+      <c r="E66">
+        <v>36</v>
+      </c>
+      <c r="F66">
+        <v>21</v>
+      </c>
+      <c r="G66">
+        <v>15</v>
+      </c>
+      <c r="H66">
+        <v>31.5</v>
+      </c>
+      <c r="I66">
+        <v>17.5</v>
+      </c>
+      <c r="J66">
+        <v>26</v>
+      </c>
+      <c r="K66">
+        <v>22.940507050000001</v>
+      </c>
+      <c r="L66">
+        <v>25.208770300000001</v>
+      </c>
+      <c r="M66">
+        <v>21.396810089999999</v>
+      </c>
+      <c r="N66">
+        <v>33.664212139999997</v>
+      </c>
+      <c r="O66">
+        <v>15.214960919999999</v>
+      </c>
+      <c r="P66">
+        <v>15.75</v>
+      </c>
+      <c r="Q66">
+        <v>20.25</v>
+      </c>
+      <c r="R66">
+        <v>15.3</v>
+      </c>
+      <c r="S66">
+        <v>10.35</v>
+      </c>
+      <c r="T66">
+        <v>11.7</v>
+      </c>
+      <c r="U66">
+        <v>13.068922000000001</v>
+      </c>
+      <c r="V66">
+        <v>14.70031341</v>
+      </c>
+      <c r="W66">
+        <v>25.696319429999999</v>
+      </c>
+      <c r="X66">
+        <v>32.378953760000002</v>
+      </c>
+      <c r="Y66">
+        <v>12.5</v>
+      </c>
+      <c r="Z66">
+        <v>24</v>
+      </c>
+      <c r="AA66">
+        <v>27.5</v>
+      </c>
+      <c r="AB66">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" t="s">
+        <v>52</v>
+      </c>
+      <c r="C67" t="s">
+        <v>47</v>
+      </c>
+      <c r="D67">
+        <v>82512.878140000001</v>
+      </c>
+      <c r="E67">
+        <v>574.0229885</v>
+      </c>
+      <c r="F67">
+        <v>482.48275860000001</v>
+      </c>
+      <c r="G67">
+        <v>479.95402300000001</v>
+      </c>
+      <c r="H67">
+        <v>851.67816089999997</v>
+      </c>
+      <c r="I67">
+        <v>1699.816092</v>
+      </c>
+      <c r="J67">
+        <v>4945.1356020000003</v>
+      </c>
+      <c r="K67">
+        <v>4535.3228390000004</v>
+      </c>
+      <c r="L67">
+        <v>5518.5103449999997</v>
+      </c>
+      <c r="M67">
+        <v>5864.7448279999999</v>
+      </c>
+      <c r="N67">
+        <v>6206.0647250000002</v>
+      </c>
+      <c r="O67">
+        <v>5003.6082969999998</v>
+      </c>
+      <c r="P67">
+        <v>4030.5403259999998</v>
+      </c>
+      <c r="Q67">
+        <v>3805.2413790000001</v>
+      </c>
+      <c r="R67">
+        <v>3920.4</v>
+      </c>
+      <c r="S67">
+        <v>4185.3103449999999</v>
+      </c>
+      <c r="T67">
+        <v>4560.3724140000004</v>
+      </c>
+      <c r="U67">
+        <v>4385.8189949999996</v>
+      </c>
+      <c r="V67">
+        <v>4712.2232059999997</v>
+      </c>
+      <c r="W67">
+        <v>4959.6308259999996</v>
+      </c>
+      <c r="X67">
+        <v>4248.2758620000004</v>
+      </c>
+      <c r="Y67">
+        <v>2596</v>
+      </c>
+      <c r="Z67">
+        <v>2356.7816090000001</v>
+      </c>
+      <c r="AA67">
+        <v>1628.5057469999999</v>
+      </c>
+      <c r="AB67">
+        <v>962.43678160000002</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" t="s">
+        <v>52</v>
+      </c>
+      <c r="C68" t="s">
+        <v>48</v>
+      </c>
+      <c r="D68">
+        <v>2259.8927330000001</v>
+      </c>
+      <c r="E68">
+        <v>18.75</v>
+      </c>
+      <c r="F68">
+        <v>27</v>
+      </c>
+      <c r="G68">
+        <v>16.875</v>
+      </c>
+      <c r="H68">
+        <v>31.125</v>
+      </c>
+      <c r="I68">
+        <v>40.5</v>
+      </c>
+      <c r="J68">
+        <v>60.208053360000001</v>
+      </c>
+      <c r="K68">
+        <v>99.285748799999993</v>
+      </c>
+      <c r="L68">
+        <v>158.55000000000001</v>
+      </c>
+      <c r="M68">
+        <v>246.75</v>
+      </c>
+      <c r="N68">
+        <v>256.0151467</v>
+      </c>
+      <c r="O68">
+        <v>198.25414459999999</v>
+      </c>
+      <c r="P68">
+        <v>151.48328240000001</v>
+      </c>
+      <c r="Q68">
+        <v>152.55000000000001</v>
+      </c>
+      <c r="R68">
+        <v>131.96250000000001</v>
+      </c>
+      <c r="S68">
+        <v>145.80000000000001</v>
+      </c>
+      <c r="T68">
+        <v>110.3625</v>
+      </c>
+      <c r="U68">
+        <v>103.677149</v>
+      </c>
+      <c r="V68">
+        <v>89.426736149999996</v>
+      </c>
+      <c r="W68">
+        <v>83.617472030000002</v>
+      </c>
+      <c r="X68">
+        <v>48.825000000000003</v>
+      </c>
+      <c r="Y68">
+        <v>29.625</v>
+      </c>
+      <c r="Z68">
+        <v>25.125</v>
+      </c>
+      <c r="AA68">
+        <v>13.125</v>
+      </c>
+      <c r="AB68">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>37</v>
+      </c>
+      <c r="B69" t="s">
+        <v>52</v>
+      </c>
+      <c r="C69" t="s">
+        <v>49</v>
+      </c>
+      <c r="D69">
+        <v>886.30290009999999</v>
+      </c>
+      <c r="E69">
+        <v>4</v>
+      </c>
+      <c r="F69">
+        <v>3.5</v>
+      </c>
+      <c r="G69">
+        <v>5</v>
+      </c>
+      <c r="H69">
+        <v>5</v>
+      </c>
+      <c r="I69">
+        <v>12.5</v>
+      </c>
+      <c r="J69">
+        <v>32.862095400000001</v>
+      </c>
+      <c r="K69">
+        <v>46.084852679999997</v>
+      </c>
+      <c r="L69">
+        <v>62.3</v>
+      </c>
+      <c r="M69">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="N69">
+        <v>94.330299229999994</v>
+      </c>
+      <c r="O69">
+        <v>110.666811</v>
+      </c>
+      <c r="P69">
+        <v>69.136624409999996</v>
+      </c>
+      <c r="Q69">
+        <v>65.7</v>
+      </c>
+      <c r="R69">
+        <v>63.9</v>
+      </c>
+      <c r="S69">
+        <v>50.4</v>
+      </c>
+      <c r="T69">
+        <v>47.25</v>
+      </c>
+      <c r="U69">
+        <v>37.778836890000001</v>
+      </c>
+      <c r="V69">
+        <v>30.36713138</v>
+      </c>
+      <c r="W69">
+        <v>21.72624914</v>
+      </c>
+      <c r="X69">
+        <v>15.4</v>
+      </c>
+      <c r="Y69">
+        <v>5.5</v>
+      </c>
+      <c r="Z69">
+        <v>7.5</v>
+      </c>
+      <c r="AA69">
+        <v>7</v>
+      </c>
+      <c r="AB69">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" t="s">
+        <v>52</v>
+      </c>
+      <c r="C70" t="s">
+        <v>50</v>
+      </c>
+      <c r="D70">
+        <v>7375.4874060000002</v>
+      </c>
+      <c r="E70">
+        <v>173</v>
+      </c>
+      <c r="F70">
+        <v>170.5</v>
+      </c>
+      <c r="G70">
+        <v>164.5</v>
+      </c>
+      <c r="H70">
+        <v>246</v>
+      </c>
+      <c r="I70">
+        <v>262.5</v>
+      </c>
+      <c r="J70">
+        <v>258.20217819999999</v>
+      </c>
+      <c r="K70">
+        <v>219.58076869999999</v>
+      </c>
+      <c r="L70">
+        <v>360.5</v>
+      </c>
+      <c r="M70">
+        <v>520.79999999999995</v>
+      </c>
+      <c r="N70">
+        <v>616.20080359999997</v>
+      </c>
+      <c r="O70">
+        <v>531.54473470000005</v>
+      </c>
+      <c r="P70">
+        <v>417.28891160000001</v>
+      </c>
+      <c r="Q70">
+        <v>385.65</v>
+      </c>
+      <c r="R70">
+        <v>378.9</v>
+      </c>
+      <c r="S70">
+        <v>297.89999999999998</v>
+      </c>
+      <c r="T70">
+        <v>297.89999999999998</v>
+      </c>
+      <c r="U70">
+        <v>270.8914327</v>
+      </c>
+      <c r="V70">
+        <v>248.29595660000001</v>
+      </c>
+      <c r="W70">
+        <v>292.73262</v>
+      </c>
+      <c r="X70">
+        <v>352.1</v>
+      </c>
+      <c r="Y70">
+        <v>239.5</v>
+      </c>
+      <c r="Z70">
+        <v>256</v>
+      </c>
+      <c r="AA70">
+        <v>204.5</v>
+      </c>
+      <c r="AB70">
+        <v>210.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>37</v>
+      </c>
+      <c r="B71" t="s">
+        <v>52</v>
+      </c>
+      <c r="C71" t="s">
+        <v>51</v>
+      </c>
+      <c r="D71">
+        <v>616.59545860000003</v>
+      </c>
+      <c r="E71">
+        <v>46.5</v>
+      </c>
+      <c r="F71">
+        <v>43.5</v>
+      </c>
+      <c r="G71">
+        <v>52</v>
+      </c>
+      <c r="H71">
+        <v>42.5</v>
+      </c>
+      <c r="I71">
+        <v>32</v>
+      </c>
+      <c r="J71">
+        <v>19.24779874</v>
+      </c>
+      <c r="K71">
+        <v>9.0362456239999993</v>
+      </c>
+      <c r="L71">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="M71">
+        <v>28</v>
+      </c>
+      <c r="N71">
+        <v>28.502680340000001</v>
+      </c>
+      <c r="O71">
+        <v>32.110577290000002</v>
+      </c>
+      <c r="P71">
+        <v>14.814990939999999</v>
+      </c>
+      <c r="Q71">
+        <v>22.5</v>
+      </c>
+      <c r="R71">
+        <v>15.3</v>
+      </c>
+      <c r="S71">
+        <v>11.25</v>
+      </c>
+      <c r="T71">
+        <v>5.4</v>
+      </c>
+      <c r="U71">
+        <v>9.4447092220000002</v>
+      </c>
+      <c r="V71">
+        <v>8.0383583069999993</v>
+      </c>
+      <c r="W71">
+        <v>13.150098160000001</v>
+      </c>
+      <c r="X71">
+        <v>29.4</v>
+      </c>
+      <c r="Y71">
+        <v>21</v>
+      </c>
+      <c r="Z71">
+        <v>43.5</v>
+      </c>
+      <c r="AA71">
+        <v>32.5</v>
+      </c>
+      <c r="AB71">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>38</v>
+      </c>
+      <c r="B72" t="s">
+        <v>46</v>
+      </c>
+      <c r="C72" t="s">
+        <v>47</v>
+      </c>
+      <c r="D72">
+        <v>73706.106039999999</v>
+      </c>
+      <c r="E72">
+        <v>694.89655170000003</v>
+      </c>
+      <c r="F72">
+        <v>485.51724139999999</v>
+      </c>
+      <c r="G72">
+        <v>475.90804600000001</v>
+      </c>
+      <c r="H72">
+        <v>672.13793099999998</v>
+      </c>
+      <c r="I72">
+        <v>1320.5057469999999</v>
+      </c>
+      <c r="J72">
+        <v>3630.173616</v>
+      </c>
+      <c r="K72">
+        <v>3946.3448279999998</v>
+      </c>
+      <c r="L72">
+        <v>3593.0997790000001</v>
+      </c>
+      <c r="M72">
+        <v>3660.7706929999999</v>
+      </c>
+      <c r="N72">
+        <v>3330.34375</v>
+      </c>
+      <c r="O72">
+        <v>3233.4706270000001</v>
+      </c>
+      <c r="P72">
+        <v>3324.2110910000001</v>
+      </c>
+      <c r="Q72">
+        <v>3374.1931030000001</v>
+      </c>
+      <c r="R72">
+        <v>3750.1655169999999</v>
+      </c>
+      <c r="S72">
+        <v>4208.9793099999997</v>
+      </c>
+      <c r="T72">
+        <v>4489.8206899999996</v>
+      </c>
+      <c r="U72">
+        <v>5405.7720010000003</v>
+      </c>
+      <c r="V72">
+        <v>5250.0184859999999</v>
+      </c>
+      <c r="W72">
+        <v>5456.9724249999999</v>
+      </c>
+      <c r="X72">
+        <v>5083.7701150000003</v>
+      </c>
+      <c r="Y72">
+        <v>2929.793103</v>
+      </c>
+      <c r="Z72">
+        <v>2426.574713</v>
+      </c>
+      <c r="AA72">
+        <v>1730.666667</v>
+      </c>
+      <c r="AB72">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" t="s">
+        <v>46</v>
+      </c>
+      <c r="C73" t="s">
+        <v>48</v>
+      </c>
+      <c r="D73">
+        <v>1824.980742</v>
+      </c>
+      <c r="E73">
+        <v>17.25</v>
+      </c>
+      <c r="F73">
+        <v>25.5</v>
+      </c>
+      <c r="G73">
+        <v>17.25</v>
+      </c>
+      <c r="H73">
+        <v>21.375</v>
+      </c>
+      <c r="I73">
+        <v>25.5</v>
+      </c>
+      <c r="J73">
+        <v>41.717337710000002</v>
+      </c>
+      <c r="K73">
+        <v>94.5</v>
+      </c>
+      <c r="L73">
+        <v>120.8789422</v>
+      </c>
+      <c r="M73">
+        <v>151.72818190000001</v>
+      </c>
+      <c r="N73">
+        <v>139.71643589999999</v>
+      </c>
+      <c r="O73">
+        <v>131.75977309999999</v>
+      </c>
+      <c r="P73">
+        <v>126.9362909</v>
+      </c>
+      <c r="Q73">
+        <v>121.83750000000001</v>
+      </c>
+      <c r="R73">
+        <v>118.46250000000001</v>
+      </c>
+      <c r="S73">
+        <v>114.075</v>
+      </c>
+      <c r="T73">
+        <v>99.5625</v>
+      </c>
+      <c r="U73">
+        <v>113.04946099999999</v>
+      </c>
+      <c r="V73">
+        <v>104.1268055</v>
+      </c>
+      <c r="W73">
+        <v>100.6300135</v>
+      </c>
+      <c r="X73">
+        <v>60.375</v>
+      </c>
+      <c r="Y73">
+        <v>26.25</v>
+      </c>
+      <c r="Z73">
+        <v>21</v>
+      </c>
+      <c r="AA73">
+        <v>16.125</v>
+      </c>
+      <c r="AB73">
+        <v>15.375</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" t="s">
+        <v>46</v>
+      </c>
+      <c r="C74" t="s">
+        <v>49</v>
+      </c>
+      <c r="D74">
+        <v>735.68394539999997</v>
+      </c>
+      <c r="E74">
+        <v>3</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
+        <v>0.5</v>
+      </c>
+      <c r="H74">
+        <v>2.5</v>
+      </c>
+      <c r="I74">
+        <v>0.5</v>
+      </c>
+      <c r="J74">
+        <v>34.949038080000001</v>
+      </c>
+      <c r="K74">
+        <v>44.55</v>
+      </c>
+      <c r="L74">
+        <v>52.892333839999999</v>
+      </c>
+      <c r="M74">
+        <v>58.616357450000002</v>
+      </c>
+      <c r="N74">
+        <v>57.894195680000003</v>
+      </c>
+      <c r="O74">
+        <v>71.743541399999998</v>
+      </c>
+      <c r="P74">
+        <v>63.644936919999999</v>
+      </c>
+      <c r="Q74">
+        <v>65.7</v>
+      </c>
+      <c r="R74">
+        <v>59.85</v>
+      </c>
+      <c r="S74">
+        <v>49.05</v>
+      </c>
+      <c r="T74">
+        <v>45.9</v>
+      </c>
+      <c r="U74">
+        <v>36.401413759999997</v>
+      </c>
+      <c r="V74">
+        <v>35.957458029999998</v>
+      </c>
+      <c r="W74">
+        <v>26.834670259999999</v>
+      </c>
+      <c r="X74">
+        <v>18.2</v>
+      </c>
+      <c r="Y74">
+        <v>5.5</v>
+      </c>
+      <c r="Z74">
+        <v>0.5</v>
+      </c>
+      <c r="AA74">
+        <v>0</v>
+      </c>
+      <c r="AB74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" t="s">
+        <v>46</v>
+      </c>
+      <c r="C75" t="s">
+        <v>50</v>
+      </c>
+      <c r="D75">
+        <v>6850.7073520000004</v>
+      </c>
+      <c r="E75">
+        <v>254.5</v>
+      </c>
+      <c r="F75">
+        <v>171.5</v>
+      </c>
+      <c r="G75">
+        <v>175.5</v>
+      </c>
+      <c r="H75">
+        <v>204</v>
+      </c>
+      <c r="I75">
+        <v>224</v>
+      </c>
+      <c r="J75">
+        <v>253.50358610000001</v>
+      </c>
+      <c r="K75">
+        <v>233.55</v>
+      </c>
+      <c r="L75">
+        <v>258.47385780000002</v>
+      </c>
+      <c r="M75">
+        <v>361.55399240000003</v>
+      </c>
+      <c r="N75">
+        <v>390.31893209999998</v>
+      </c>
+      <c r="O75">
+        <v>406.54673459999998</v>
+      </c>
+      <c r="P75">
+        <v>391.76994500000001</v>
+      </c>
+      <c r="Q75">
+        <v>363.15</v>
+      </c>
+      <c r="R75">
+        <v>366.75</v>
+      </c>
+      <c r="S75">
+        <v>292.05</v>
+      </c>
+      <c r="T75">
+        <v>292.05</v>
+      </c>
+      <c r="U75">
+        <v>284.54626250000001</v>
+      </c>
+      <c r="V75">
+        <v>297.14843789999998</v>
+      </c>
+      <c r="W75">
+        <v>357.79560350000003</v>
+      </c>
+      <c r="X75">
+        <v>378</v>
+      </c>
+      <c r="Y75">
+        <v>260</v>
+      </c>
+      <c r="Z75">
+        <v>237</v>
+      </c>
+      <c r="AA75">
+        <v>200.5</v>
+      </c>
+      <c r="AB75">
+        <v>196.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>38</v>
+      </c>
+      <c r="B76" t="s">
+        <v>46</v>
+      </c>
+      <c r="C76" t="s">
+        <v>51</v>
+      </c>
+      <c r="D76">
+        <v>435.4696179</v>
+      </c>
+      <c r="E76">
+        <v>41</v>
+      </c>
+      <c r="F76">
+        <v>22.5</v>
+      </c>
+      <c r="G76">
+        <v>28</v>
+      </c>
+      <c r="H76">
+        <v>26</v>
+      </c>
+      <c r="I76">
+        <v>23</v>
+      </c>
+      <c r="J76">
+        <v>20.674078860000002</v>
+      </c>
+      <c r="K76">
+        <v>12.6</v>
+      </c>
+      <c r="L76">
+        <v>13.472575600000001</v>
+      </c>
+      <c r="M76">
+        <v>18.674237770000001</v>
+      </c>
+      <c r="N76">
+        <v>20.076213020000001</v>
+      </c>
+      <c r="O76">
+        <v>13.79683489</v>
+      </c>
+      <c r="P76">
+        <v>13.20043136</v>
+      </c>
+      <c r="Q76">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="R76">
+        <v>12.6</v>
+      </c>
+      <c r="S76">
+        <v>9</v>
+      </c>
+      <c r="T76">
+        <v>6.75</v>
+      </c>
+      <c r="U76">
+        <v>13.330095180000001</v>
+      </c>
+      <c r="V76">
+        <v>10.987001060000001</v>
+      </c>
+      <c r="W76">
+        <v>14.908150150000001</v>
+      </c>
+      <c r="X76">
+        <v>23.8</v>
+      </c>
+      <c r="Y76">
+        <v>12.5</v>
+      </c>
+      <c r="Z76">
+        <v>20.5</v>
+      </c>
+      <c r="AA76">
+        <v>20.5</v>
+      </c>
+      <c r="AB76">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>38</v>
+      </c>
+      <c r="B77" t="s">
+        <v>52</v>
+      </c>
+      <c r="C77" t="s">
+        <v>47</v>
+      </c>
+      <c r="D77">
+        <v>77315.691260000007</v>
+      </c>
+      <c r="E77">
+        <v>548.22988510000005</v>
+      </c>
+      <c r="F77">
+        <v>423.3103448</v>
+      </c>
+      <c r="G77">
+        <v>477.4252874</v>
+      </c>
+      <c r="H77">
+        <v>862.80459770000004</v>
+      </c>
+      <c r="I77">
+        <v>1736.229885</v>
+      </c>
+      <c r="J77">
+        <v>4694.6482759999999</v>
+      </c>
+      <c r="K77">
+        <v>4369.2</v>
+      </c>
+      <c r="L77">
+        <v>4942.1609200000003</v>
+      </c>
+      <c r="M77">
+        <v>5112.0919540000004</v>
+      </c>
+      <c r="N77">
+        <v>5723.8436780000002</v>
+      </c>
+      <c r="O77">
+        <v>4195.1514669999997</v>
+      </c>
+      <c r="P77">
+        <v>3616.091954</v>
+      </c>
+      <c r="Q77">
+        <v>3442.9422399999999</v>
+      </c>
+      <c r="R77">
+        <v>3574.5819809999998</v>
+      </c>
+      <c r="S77">
+        <v>3844.339219</v>
+      </c>
+      <c r="T77">
+        <v>4043.2965519999998</v>
+      </c>
+      <c r="U77">
+        <v>4310.458149</v>
+      </c>
+      <c r="V77">
+        <v>4912.8041350000003</v>
+      </c>
+      <c r="W77">
+        <v>5225.6209669999998</v>
+      </c>
+      <c r="X77">
+        <v>3947.3563220000001</v>
+      </c>
+      <c r="Y77">
+        <v>2531.2643680000001</v>
+      </c>
+      <c r="Z77">
+        <v>2264.2298850000002</v>
+      </c>
+      <c r="AA77">
+        <v>1552.6436779999999</v>
+      </c>
+      <c r="AB77">
+        <v>964.96551720000002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" t="s">
+        <v>52</v>
+      </c>
+      <c r="C78" t="s">
+        <v>48</v>
+      </c>
+      <c r="D78">
+        <v>2022.2004449999999</v>
+      </c>
+      <c r="E78">
+        <v>22.5</v>
+      </c>
+      <c r="F78">
+        <v>26.25</v>
+      </c>
+      <c r="G78">
+        <v>14.625</v>
+      </c>
+      <c r="H78">
+        <v>16.875</v>
+      </c>
+      <c r="I78">
+        <v>32.25</v>
+      </c>
+      <c r="J78">
+        <v>43.875</v>
+      </c>
+      <c r="K78">
+        <v>94.5</v>
+      </c>
+      <c r="L78">
+        <v>138.6</v>
+      </c>
+      <c r="M78">
+        <v>207.375</v>
+      </c>
+      <c r="N78">
+        <v>227.85</v>
+      </c>
+      <c r="O78">
+        <v>168.85240150000001</v>
+      </c>
+      <c r="P78">
+        <v>133.875</v>
+      </c>
+      <c r="Q78">
+        <v>138.31567699999999</v>
+      </c>
+      <c r="R78">
+        <v>120.3060443</v>
+      </c>
+      <c r="S78">
+        <v>123.4210724</v>
+      </c>
+      <c r="T78">
+        <v>105.3</v>
+      </c>
+      <c r="U78">
+        <v>104.9497916</v>
+      </c>
+      <c r="V78">
+        <v>97.039237349999993</v>
+      </c>
+      <c r="W78">
+        <v>87.766220930000003</v>
+      </c>
+      <c r="X78">
+        <v>50.924999999999997</v>
+      </c>
+      <c r="Y78">
+        <v>21</v>
+      </c>
+      <c r="Z78">
+        <v>19.875</v>
+      </c>
+      <c r="AA78">
+        <v>12.375</v>
+      </c>
+      <c r="AB78">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>38</v>
+      </c>
+      <c r="B79" t="s">
+        <v>52</v>
+      </c>
+      <c r="C79" t="s">
+        <v>49</v>
+      </c>
+      <c r="D79">
+        <v>827.90290100000004</v>
+      </c>
+      <c r="E79">
+        <v>3</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79">
+        <v>3</v>
+      </c>
+      <c r="H79">
+        <v>2.5</v>
+      </c>
+      <c r="I79">
+        <v>0.5</v>
+      </c>
+      <c r="J79">
+        <v>29.7</v>
+      </c>
+      <c r="K79">
+        <v>47.7</v>
+      </c>
+      <c r="L79">
+        <v>61.6</v>
+      </c>
+      <c r="M79">
+        <v>70</v>
+      </c>
+      <c r="N79">
+        <v>84</v>
+      </c>
+      <c r="O79">
+        <v>102.0403002</v>
+      </c>
+      <c r="P79">
+        <v>58</v>
+      </c>
+      <c r="Q79">
+        <v>67.393317550000006</v>
+      </c>
+      <c r="R79">
+        <v>64.344475680000002</v>
+      </c>
+      <c r="S79">
+        <v>53.899830659999999</v>
+      </c>
+      <c r="T79">
+        <v>48.6</v>
+      </c>
+      <c r="U79">
+        <v>37.106848569999997</v>
+      </c>
+      <c r="V79">
+        <v>34.603138899999998</v>
+      </c>
+      <c r="W79">
+        <v>31.91498941</v>
+      </c>
+      <c r="X79">
+        <v>14</v>
+      </c>
+      <c r="Y79">
+        <v>5.5</v>
+      </c>
+      <c r="Z79">
+        <v>5.5</v>
+      </c>
+      <c r="AA79">
+        <v>1.5</v>
+      </c>
+      <c r="AB79">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>38</v>
+      </c>
+      <c r="B80" t="s">
+        <v>52</v>
+      </c>
+      <c r="C80" t="s">
+        <v>50</v>
+      </c>
+      <c r="D80">
+        <v>7266.7240849999998</v>
+      </c>
+      <c r="E80">
+        <v>258</v>
+      </c>
+      <c r="F80">
+        <v>188.5</v>
+      </c>
+      <c r="G80">
+        <v>170.5</v>
+      </c>
+      <c r="H80">
+        <v>243.5</v>
+      </c>
+      <c r="I80">
+        <v>219.5</v>
+      </c>
+      <c r="J80">
+        <v>230.85</v>
+      </c>
+      <c r="K80">
+        <v>229.95</v>
+      </c>
+      <c r="L80">
+        <v>350</v>
+      </c>
+      <c r="M80">
+        <v>447.3</v>
+      </c>
+      <c r="N80">
+        <v>551.6</v>
+      </c>
+      <c r="O80">
+        <v>453.51244530000002</v>
+      </c>
+      <c r="P80">
+        <v>389.5</v>
+      </c>
+      <c r="Q80">
+        <v>369.75252599999999</v>
+      </c>
+      <c r="R80">
+        <v>372.92608089999999</v>
+      </c>
+      <c r="S80">
+        <v>295.25659450000001</v>
+      </c>
+      <c r="T80">
+        <v>317.7</v>
+      </c>
+      <c r="U80">
+        <v>278.07782909999997</v>
+      </c>
+      <c r="V80">
+        <v>307.91778670000002</v>
+      </c>
+      <c r="W80">
+        <v>345.08082300000001</v>
+      </c>
+      <c r="X80">
+        <v>349.3</v>
+      </c>
+      <c r="Y80">
+        <v>238</v>
+      </c>
+      <c r="Z80">
+        <v>256.5</v>
+      </c>
+      <c r="AA80">
+        <v>198.5</v>
+      </c>
+      <c r="AB80">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>38</v>
+      </c>
+      <c r="B81" t="s">
+        <v>52</v>
+      </c>
+      <c r="C81" t="s">
+        <v>51</v>
+      </c>
+      <c r="D81">
+        <v>484.99597740000002</v>
+      </c>
+      <c r="E81">
+        <v>52</v>
+      </c>
+      <c r="F81">
+        <v>24</v>
+      </c>
+      <c r="G81">
+        <v>28.5</v>
+      </c>
+      <c r="H81">
+        <v>26</v>
+      </c>
+      <c r="I81">
+        <v>23</v>
+      </c>
+      <c r="J81">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="K81">
+        <v>9</v>
+      </c>
+      <c r="L81">
+        <v>17.5</v>
+      </c>
+      <c r="M81">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="N81">
+        <v>24.5</v>
+      </c>
+      <c r="O81">
+        <v>21.055934959999998</v>
+      </c>
+      <c r="P81">
+        <v>16</v>
+      </c>
+      <c r="Q81">
+        <v>17.75904989</v>
+      </c>
+      <c r="R81">
+        <v>14.95329364</v>
+      </c>
+      <c r="S81">
+        <v>10.016782689999999</v>
+      </c>
+      <c r="T81">
+        <v>8.1</v>
+      </c>
+      <c r="U81">
+        <v>14.30625487</v>
+      </c>
+      <c r="V81">
+        <v>14.04185347</v>
+      </c>
+      <c r="W81">
+        <v>13.962807870000001</v>
+      </c>
+      <c r="X81">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="Y81">
+        <v>13</v>
+      </c>
+      <c r="Z81">
+        <v>31</v>
+      </c>
+      <c r="AA81">
+        <v>27.5</v>
+      </c>
+      <c r="AB81">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>39</v>
+      </c>
+      <c r="B82" t="s">
+        <v>46</v>
+      </c>
+      <c r="C82" t="s">
+        <v>47</v>
+      </c>
+      <c r="D82">
+        <v>63093.85873</v>
+      </c>
+      <c r="E82">
+        <v>626.62068969999996</v>
+      </c>
+      <c r="F82">
+        <v>466.29885059999998</v>
+      </c>
+      <c r="G82">
+        <v>406.62068970000001</v>
+      </c>
+      <c r="H82">
+        <v>438.98850570000002</v>
+      </c>
+      <c r="I82">
+        <v>625.60919539999998</v>
+      </c>
+      <c r="J82">
+        <v>1582.9885059999999</v>
+      </c>
+      <c r="K82">
+        <v>2926.477038</v>
+      </c>
+      <c r="L82">
+        <v>3168.0578909999999</v>
+      </c>
+      <c r="M82">
+        <v>2817.1037259999998</v>
+      </c>
+      <c r="N82">
+        <v>2608.004852</v>
+      </c>
+      <c r="O82">
+        <v>2919.6979289999999</v>
+      </c>
+      <c r="P82">
+        <v>2921.1252650000001</v>
+      </c>
+      <c r="Q82">
+        <v>3092.5660229999999</v>
+      </c>
+      <c r="R82">
+        <v>3365.5448280000001</v>
+      </c>
+      <c r="S82">
+        <v>4131.1448280000004</v>
+      </c>
+      <c r="T82">
+        <v>4804.8</v>
+      </c>
+      <c r="U82">
+        <v>5399.0369300000002</v>
+      </c>
+      <c r="V82">
+        <v>4744.8112300000003</v>
+      </c>
+      <c r="W82">
+        <v>4475.6363430000001</v>
+      </c>
+      <c r="X82">
+        <v>4296.541502</v>
+      </c>
+      <c r="Y82">
+        <v>2564.1379310000002</v>
+      </c>
+      <c r="Z82">
+        <v>1902.114943</v>
+      </c>
+      <c r="AA82">
+        <v>1657.333333</v>
+      </c>
+      <c r="AB82">
+        <v>1152.5977009999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>39</v>
+      </c>
+      <c r="B83" t="s">
+        <v>46</v>
+      </c>
+      <c r="C83" t="s">
+        <v>48</v>
+      </c>
+      <c r="D83">
+        <v>1569.603492</v>
+      </c>
+      <c r="E83">
+        <v>7.125</v>
+      </c>
+      <c r="F83">
+        <v>12.375</v>
+      </c>
+      <c r="G83">
+        <v>9.75</v>
+      </c>
+      <c r="H83">
+        <v>18.375</v>
+      </c>
+      <c r="I83">
+        <v>39.375</v>
+      </c>
+      <c r="J83">
+        <v>49.5</v>
+      </c>
+      <c r="K83">
+        <v>88.618047149999995</v>
+      </c>
+      <c r="L83">
+        <v>133.93514400000001</v>
+      </c>
+      <c r="M83">
+        <v>152.43624410000001</v>
+      </c>
+      <c r="N83">
+        <v>161.6673667</v>
+      </c>
+      <c r="O83">
+        <v>110.1668576</v>
+      </c>
+      <c r="P83">
+        <v>96.176957849999994</v>
+      </c>
+      <c r="Q83">
+        <v>83.277463580000003</v>
+      </c>
+      <c r="R83">
+        <v>98.887500000000003</v>
+      </c>
+      <c r="S83">
+        <v>88.762500000000003</v>
+      </c>
+      <c r="T83">
+        <v>83.025000000000006</v>
+      </c>
+      <c r="U83">
+        <v>83.996882330000005</v>
+      </c>
+      <c r="V83">
+        <v>69.993616220000007</v>
+      </c>
+      <c r="W83">
+        <v>70.574397619999999</v>
+      </c>
+      <c r="X83">
+        <v>41.460515360000002</v>
+      </c>
+      <c r="Y83">
+        <v>21</v>
+      </c>
+      <c r="Z83">
+        <v>18</v>
+      </c>
+      <c r="AA83">
+        <v>14.625</v>
+      </c>
+      <c r="AB83">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>39</v>
+      </c>
+      <c r="B84" t="s">
+        <v>46</v>
+      </c>
+      <c r="C84" t="s">
+        <v>49</v>
+      </c>
+      <c r="D84">
+        <v>646.95912169999997</v>
+      </c>
+      <c r="E84">
+        <v>2.5</v>
+      </c>
+      <c r="F84">
+        <v>0.5</v>
+      </c>
+      <c r="G84">
+        <v>0.5</v>
+      </c>
+      <c r="H84">
+        <v>1.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>42</v>
+      </c>
+      <c r="K84">
+        <v>48.570629250000003</v>
+      </c>
+      <c r="L84">
+        <v>45.105306220000003</v>
+      </c>
+      <c r="M84">
+        <v>61.367248029999999</v>
+      </c>
+      <c r="N84">
+        <v>64.031519369999998</v>
+      </c>
+      <c r="O84">
+        <v>52.742074979999998</v>
+      </c>
+      <c r="P84">
+        <v>62.44947449</v>
+      </c>
+      <c r="Q84">
+        <v>56.209408340000003</v>
+      </c>
+      <c r="R84">
+        <v>54.9</v>
+      </c>
+      <c r="S84">
+        <v>45</v>
+      </c>
+      <c r="T84">
+        <v>24.75</v>
+      </c>
+      <c r="U84">
+        <v>20.705113860000001</v>
+      </c>
+      <c r="V84">
+        <v>24.651839679999998</v>
+      </c>
+      <c r="W84">
+        <v>21.674534099999999</v>
+      </c>
+      <c r="X84">
+        <v>10.801973350000001</v>
+      </c>
+      <c r="Y84">
+        <v>2</v>
+      </c>
+      <c r="Z84">
+        <v>2.5</v>
+      </c>
+      <c r="AA84">
+        <v>0</v>
+      </c>
+      <c r="AB84">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>39</v>
+      </c>
+      <c r="B85" t="s">
+        <v>46</v>
+      </c>
+      <c r="C85" t="s">
+        <v>50</v>
+      </c>
+      <c r="D85">
+        <v>6690.0395710000003</v>
+      </c>
+      <c r="E85">
+        <v>150</v>
+      </c>
+      <c r="F85">
+        <v>173</v>
+      </c>
+      <c r="G85">
+        <v>176</v>
+      </c>
+      <c r="H85">
+        <v>186.5</v>
+      </c>
+      <c r="I85">
+        <v>217.5</v>
+      </c>
+      <c r="J85">
+        <v>263.5</v>
+      </c>
+      <c r="K85">
+        <v>247.05637379999999</v>
+      </c>
+      <c r="L85">
+        <v>254.9830576</v>
+      </c>
+      <c r="M85">
+        <v>383.91350369999998</v>
+      </c>
+      <c r="N85">
+        <v>439.42241150000001</v>
+      </c>
+      <c r="O85">
+        <v>451.51159510000002</v>
+      </c>
+      <c r="P85">
+        <v>436.66960790000002</v>
+      </c>
+      <c r="Q85">
+        <v>363.51822279999999</v>
+      </c>
+      <c r="R85">
+        <v>335.7</v>
+      </c>
+      <c r="S85">
+        <v>309.14999999999998</v>
+      </c>
+      <c r="T85">
+        <v>265.5</v>
+      </c>
+      <c r="U85">
+        <v>245.16737090000001</v>
+      </c>
+      <c r="V85">
+        <v>244.3173396</v>
+      </c>
+      <c r="W85">
+        <v>336.7482493</v>
+      </c>
+      <c r="X85">
+        <v>351.38183889999999</v>
+      </c>
+      <c r="Y85">
+        <v>280.5</v>
+      </c>
+      <c r="Z85">
+        <v>214</v>
+      </c>
+      <c r="AA85">
+        <v>176</v>
+      </c>
+      <c r="AB85">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" t="s">
+        <v>46</v>
+      </c>
+      <c r="C86" t="s">
+        <v>51</v>
+      </c>
+      <c r="D86">
+        <v>442.9027648</v>
+      </c>
+      <c r="E86">
+        <v>23</v>
+      </c>
+      <c r="F86">
+        <v>22</v>
+      </c>
+      <c r="G86">
+        <v>36.5</v>
+      </c>
+      <c r="H86">
+        <v>26</v>
+      </c>
+      <c r="I86">
+        <v>24.5</v>
+      </c>
+      <c r="J86">
+        <v>15.5</v>
+      </c>
+      <c r="K86">
+        <v>7.0053792189999999</v>
+      </c>
+      <c r="L86">
+        <v>9.6654227620000004</v>
+      </c>
+      <c r="M86">
+        <v>24.546899209999999</v>
+      </c>
+      <c r="N86">
+        <v>22.973140539999999</v>
+      </c>
+      <c r="O86">
+        <v>17.744997189999999</v>
+      </c>
+      <c r="P86">
+        <v>11.441125100000001</v>
+      </c>
+      <c r="Q86">
+        <v>18.890047070000001</v>
+      </c>
+      <c r="R86">
+        <v>14.4</v>
+      </c>
+      <c r="S86">
+        <v>15.3</v>
+      </c>
+      <c r="T86">
+        <v>6.3</v>
+      </c>
+      <c r="U86">
+        <v>8.4702738499999999</v>
+      </c>
+      <c r="V86">
+        <v>7.0433827649999996</v>
+      </c>
+      <c r="W86">
+        <v>17.445356709999999</v>
+      </c>
+      <c r="X86">
+        <v>33.676740440000003</v>
+      </c>
+      <c r="Y86">
+        <v>17.5</v>
+      </c>
+      <c r="Z86">
+        <v>32.5</v>
+      </c>
+      <c r="AA86">
+        <v>20</v>
+      </c>
+      <c r="AB86">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>39</v>
+      </c>
+      <c r="B87" t="s">
+        <v>52</v>
+      </c>
+      <c r="C87" t="s">
+        <v>47</v>
+      </c>
+      <c r="D87">
+        <v>67342.157860000007</v>
+      </c>
+      <c r="E87">
+        <v>452.13793099999998</v>
+      </c>
+      <c r="F87">
+        <v>334.29885059999998</v>
+      </c>
+      <c r="G87">
+        <v>404.59770109999999</v>
+      </c>
+      <c r="H87">
+        <v>762.16091949999998</v>
+      </c>
+      <c r="I87">
+        <v>1599.1724139999999</v>
+      </c>
+      <c r="J87">
+        <v>4182.1241380000001</v>
+      </c>
+      <c r="K87">
+        <v>4343.7103450000004</v>
+      </c>
+      <c r="L87">
+        <v>4612.0909519999996</v>
+      </c>
+      <c r="M87">
+        <v>3961.434671</v>
+      </c>
+      <c r="N87">
+        <v>3653.1802090000001</v>
+      </c>
+      <c r="O87">
+        <v>3344.2316860000001</v>
+      </c>
+      <c r="P87">
+        <v>3144.7356319999999</v>
+      </c>
+      <c r="Q87">
+        <v>3176.884685</v>
+      </c>
+      <c r="R87">
+        <v>3317.7468330000002</v>
+      </c>
+      <c r="S87">
+        <v>3548.3218390000002</v>
+      </c>
+      <c r="T87">
+        <v>3714.9000540000002</v>
+      </c>
+      <c r="U87">
+        <v>4029.4878659999999</v>
+      </c>
+      <c r="V87">
+        <v>4128.2455840000002</v>
+      </c>
+      <c r="W87">
+        <v>4282.8840540000001</v>
+      </c>
+      <c r="X87">
+        <v>3604.662069</v>
+      </c>
+      <c r="Y87">
+        <v>2377.0114939999999</v>
+      </c>
+      <c r="Z87">
+        <v>2189.3793099999998</v>
+      </c>
+      <c r="AA87">
+        <v>1344.275862</v>
+      </c>
+      <c r="AB87">
+        <v>834.48275860000001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>39</v>
+      </c>
+      <c r="B88" t="s">
+        <v>52</v>
+      </c>
+      <c r="C88" t="s">
+        <v>48</v>
+      </c>
+      <c r="D88">
+        <v>1831.767306</v>
+      </c>
+      <c r="E88">
+        <v>20.625</v>
+      </c>
+      <c r="F88">
+        <v>18.75</v>
+      </c>
+      <c r="G88">
+        <v>24.375</v>
+      </c>
+      <c r="H88">
+        <v>12</v>
+      </c>
+      <c r="I88">
+        <v>40.5</v>
+      </c>
+      <c r="J88">
+        <v>44.55</v>
+      </c>
+      <c r="K88">
+        <v>81.337500000000006</v>
+      </c>
+      <c r="L88">
+        <v>120.10328320000001</v>
+      </c>
+      <c r="M88">
+        <v>159.4810487</v>
+      </c>
+      <c r="N88">
+        <v>138.23699719999999</v>
+      </c>
+      <c r="O88">
+        <v>127.5474143</v>
+      </c>
+      <c r="P88">
+        <v>112.875</v>
+      </c>
+      <c r="Q88">
+        <v>131.2833287</v>
+      </c>
+      <c r="R88">
+        <v>125.7138884</v>
+      </c>
+      <c r="S88">
+        <v>128.625</v>
+      </c>
+      <c r="T88">
+        <v>107.8468239</v>
+      </c>
+      <c r="U88">
+        <v>107.4313776</v>
+      </c>
+      <c r="V88">
+        <v>95.293924349999998</v>
+      </c>
+      <c r="W88">
+        <v>87.44171978</v>
+      </c>
+      <c r="X88">
+        <v>42</v>
+      </c>
+      <c r="Y88">
+        <v>25.5</v>
+      </c>
+      <c r="Z88">
+        <v>37.875</v>
+      </c>
+      <c r="AA88">
+        <v>13.875</v>
+      </c>
+      <c r="AB88">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89" t="s">
+        <v>52</v>
+      </c>
+      <c r="C89" t="s">
+        <v>49</v>
+      </c>
+      <c r="D89">
+        <v>701.30360029999997</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>1.5</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="I89">
+        <v>0.5</v>
+      </c>
+      <c r="J89">
+        <v>21.6</v>
+      </c>
+      <c r="K89">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="L89">
+        <v>32.819742869999999</v>
+      </c>
+      <c r="M89">
+        <v>47.980623199999997</v>
+      </c>
+      <c r="N89">
+        <v>60.752199879999999</v>
+      </c>
+      <c r="O89">
+        <v>76.528448580000003</v>
+      </c>
+      <c r="P89">
+        <v>57.5</v>
+      </c>
+      <c r="Q89">
+        <v>70.590127719999998</v>
+      </c>
+      <c r="R89">
+        <v>59.619414489999997</v>
+      </c>
+      <c r="S89">
+        <v>56</v>
+      </c>
+      <c r="T89">
+        <v>47.617614039999999</v>
+      </c>
+      <c r="U89">
+        <v>42.332639049999997</v>
+      </c>
+      <c r="V89">
+        <v>32.368531959999999</v>
+      </c>
+      <c r="W89">
+        <v>32.69425854</v>
+      </c>
+      <c r="X89">
+        <v>11.2</v>
+      </c>
+      <c r="Y89">
+        <v>0.5</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+      <c r="AA89">
+        <v>6.5</v>
+      </c>
+      <c r="AB89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>39</v>
+      </c>
+      <c r="B90" t="s">
+        <v>52</v>
+      </c>
+      <c r="C90" t="s">
+        <v>50</v>
+      </c>
+      <c r="D90">
+        <v>6675.7400589999997</v>
+      </c>
+      <c r="E90">
+        <v>160</v>
+      </c>
+      <c r="F90">
+        <v>178</v>
+      </c>
+      <c r="G90">
+        <v>184.5</v>
+      </c>
+      <c r="H90">
+        <v>218.5</v>
+      </c>
+      <c r="I90">
+        <v>169.5</v>
+      </c>
+      <c r="J90">
+        <v>215.55</v>
+      </c>
+      <c r="K90">
+        <v>225.9</v>
+      </c>
+      <c r="L90">
+        <v>291.98253999999997</v>
+      </c>
+      <c r="M90">
+        <v>360.94514270000002</v>
+      </c>
+      <c r="N90">
+        <v>393.85960089999998</v>
+      </c>
+      <c r="O90">
+        <v>375.6396398</v>
+      </c>
+      <c r="P90">
+        <v>360.5</v>
+      </c>
+      <c r="Q90">
+        <v>386.81482149999999</v>
+      </c>
+      <c r="R90">
+        <v>386.06014299999998</v>
+      </c>
+      <c r="S90">
+        <v>271.5</v>
+      </c>
+      <c r="T90">
+        <v>336.62352900000002</v>
+      </c>
+      <c r="U90">
+        <v>304.2043132</v>
+      </c>
+      <c r="V90">
+        <v>300.49592360000003</v>
+      </c>
+      <c r="W90">
+        <v>342.36440540000001</v>
+      </c>
+      <c r="X90">
+        <v>356.3</v>
+      </c>
+      <c r="Y90">
+        <v>257</v>
+      </c>
+      <c r="Z90">
+        <v>239.5</v>
+      </c>
+      <c r="AA90">
+        <v>191</v>
+      </c>
+      <c r="AB90">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>39</v>
+      </c>
+      <c r="B91" t="s">
+        <v>52</v>
+      </c>
+      <c r="C91" t="s">
+        <v>51</v>
+      </c>
+      <c r="D91">
+        <v>414.76253910000003</v>
+      </c>
+      <c r="E91">
+        <v>36</v>
+      </c>
+      <c r="F91">
+        <v>19.5</v>
+      </c>
+      <c r="G91">
+        <v>12</v>
+      </c>
+      <c r="H91">
+        <v>22</v>
+      </c>
+      <c r="I91">
+        <v>19.5</v>
+      </c>
+      <c r="J91">
+        <v>20.25</v>
+      </c>
+      <c r="K91">
+        <v>13.95</v>
+      </c>
+      <c r="L91">
+        <v>22.06844779</v>
+      </c>
+      <c r="M91">
+        <v>14.72132757</v>
+      </c>
+      <c r="N91">
+        <v>20.07911691</v>
+      </c>
+      <c r="O91">
+        <v>18.506879720000001</v>
+      </c>
+      <c r="P91">
+        <v>14.5</v>
+      </c>
+      <c r="Q91">
+        <v>20.03233354</v>
+      </c>
+      <c r="R91">
+        <v>15.149195479999999</v>
+      </c>
+      <c r="S91">
+        <v>10</v>
+      </c>
+      <c r="T91">
+        <v>10.37215355</v>
+      </c>
+      <c r="U91">
+        <v>14.76719967</v>
+      </c>
+      <c r="V91">
+        <v>12.07781043</v>
+      </c>
+      <c r="W91">
+        <v>14.188074459999999</v>
+      </c>
+      <c r="X91">
+        <v>9.1</v>
+      </c>
+      <c r="Y91">
+        <v>5</v>
+      </c>
+      <c r="Z91">
+        <v>20.5</v>
+      </c>
+      <c r="AA91">
+        <v>17</v>
+      </c>
+      <c r="AB91">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>41</v>
+      </c>
+      <c r="B92" t="s">
+        <v>46</v>
+      </c>
+      <c r="C92" t="s">
+        <v>47</v>
+      </c>
+      <c r="D92">
+        <v>59835.396339999999</v>
+      </c>
+      <c r="E92">
+        <v>646.34482760000003</v>
+      </c>
+      <c r="F92">
+        <v>481.4712644</v>
+      </c>
+      <c r="G92">
+        <v>446.06896549999999</v>
+      </c>
+      <c r="H92">
+        <v>479.4482759</v>
+      </c>
+      <c r="I92">
+        <v>619.03448279999998</v>
+      </c>
+      <c r="J92">
+        <v>1429.2413790000001</v>
+      </c>
+      <c r="K92">
+        <v>2883.0620690000001</v>
+      </c>
+      <c r="L92">
+        <v>2804.578356</v>
+      </c>
+      <c r="M92">
+        <v>2579.8025010000001</v>
+      </c>
+      <c r="N92">
+        <v>2455.2169859999999</v>
+      </c>
+      <c r="O92">
+        <v>2729.9483909999999</v>
+      </c>
+      <c r="P92">
+        <v>3128.855172</v>
+      </c>
+      <c r="Q92">
+        <v>3175.2827590000002</v>
+      </c>
+      <c r="R92">
+        <v>3506.6482759999999</v>
+      </c>
+      <c r="S92">
+        <v>4338.7034480000002</v>
+      </c>
+      <c r="T92">
+        <v>5442.9517239999996</v>
+      </c>
+      <c r="U92">
+        <v>3742.7310339999999</v>
+      </c>
+      <c r="V92">
+        <v>4080.075386</v>
+      </c>
+      <c r="W92">
+        <v>4103.1322890000001</v>
+      </c>
+      <c r="X92">
+        <v>3481.0516280000002</v>
+      </c>
+      <c r="Y92">
+        <v>2678.4367820000002</v>
+      </c>
+      <c r="Z92">
+        <v>1919.816092</v>
+      </c>
+      <c r="AA92">
+        <v>1635.5862070000001</v>
+      </c>
+      <c r="AB92">
+        <v>1047.908046</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>41</v>
+      </c>
+      <c r="B93" t="s">
+        <v>46</v>
+      </c>
+      <c r="C93" t="s">
+        <v>48</v>
+      </c>
+      <c r="D93">
+        <v>1525.7600890000001</v>
+      </c>
+      <c r="E93">
+        <v>11.25</v>
+      </c>
+      <c r="F93">
+        <v>3.75</v>
+      </c>
+      <c r="G93">
+        <v>13.5</v>
+      </c>
+      <c r="H93">
+        <v>22.5</v>
+      </c>
+      <c r="I93">
+        <v>41.25</v>
+      </c>
+      <c r="J93">
+        <v>49.5</v>
+      </c>
+      <c r="K93">
+        <v>87.75</v>
+      </c>
+      <c r="L93">
+        <v>82.580657849999994</v>
+      </c>
+      <c r="M93">
+        <v>111.5742017</v>
+      </c>
+      <c r="N93">
+        <v>128.3215893</v>
+      </c>
+      <c r="O93">
+        <v>98.326698449999995</v>
+      </c>
+      <c r="P93">
+        <v>99.9</v>
+      </c>
+      <c r="Q93">
+        <v>97.2</v>
+      </c>
+      <c r="R93">
+        <v>103.27500000000001</v>
+      </c>
+      <c r="S93">
+        <v>113.4</v>
+      </c>
+      <c r="T93">
+        <v>114.75</v>
+      </c>
+      <c r="U93">
+        <v>74.7</v>
+      </c>
+      <c r="V93">
+        <v>66.072003409999994</v>
+      </c>
+      <c r="W93">
+        <v>91.396580999999998</v>
+      </c>
+      <c r="X93">
+        <v>30.76335679</v>
+      </c>
+      <c r="Y93">
+        <v>26.25</v>
+      </c>
+      <c r="Z93">
+        <v>21</v>
+      </c>
+      <c r="AA93">
+        <v>10.5</v>
+      </c>
+      <c r="AB93">
+        <v>26.25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>41</v>
+      </c>
+      <c r="B94" t="s">
+        <v>46</v>
+      </c>
+      <c r="C94" t="s">
+        <v>49</v>
+      </c>
+      <c r="D94">
+        <v>589.89796969999998</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>25</v>
+      </c>
+      <c r="K94">
+        <v>48.6</v>
+      </c>
+      <c r="L94">
+        <v>37.369833030000002</v>
+      </c>
+      <c r="M94">
+        <v>46.776813089999997</v>
+      </c>
+      <c r="N94">
+        <v>43.973130300000001</v>
+      </c>
+      <c r="O94">
+        <v>56.649126690000003</v>
+      </c>
+      <c r="P94">
+        <v>52.2</v>
+      </c>
+      <c r="Q94">
+        <v>45.9</v>
+      </c>
+      <c r="R94">
+        <v>45</v>
+      </c>
+      <c r="S94">
+        <v>62.1</v>
+      </c>
+      <c r="T94">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="U94">
+        <v>25.2</v>
+      </c>
+      <c r="V94">
+        <v>16.291726870000002</v>
+      </c>
+      <c r="W94">
+        <v>20.032127339999999</v>
+      </c>
+      <c r="X94">
+        <v>12.00521241</v>
+      </c>
+      <c r="Y94">
+        <v>3</v>
+      </c>
+      <c r="Z94">
+        <v>8</v>
+      </c>
+      <c r="AA94">
+        <v>3</v>
+      </c>
+      <c r="AB94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>41</v>
+      </c>
+      <c r="B95" t="s">
+        <v>46</v>
+      </c>
+      <c r="C95" t="s">
+        <v>50</v>
+      </c>
+      <c r="D95">
+        <v>7216.3816850000003</v>
+      </c>
+      <c r="E95">
+        <v>213</v>
+      </c>
+      <c r="F95">
+        <v>218</v>
+      </c>
+      <c r="G95">
+        <v>210</v>
+      </c>
+      <c r="H95">
+        <v>181</v>
+      </c>
+      <c r="I95">
+        <v>229</v>
+      </c>
+      <c r="J95">
+        <v>303</v>
+      </c>
+      <c r="K95">
+        <v>283.5</v>
+      </c>
+      <c r="L95">
+        <v>207.53603699999999</v>
+      </c>
+      <c r="M95">
+        <v>340.47385270000001</v>
+      </c>
+      <c r="N95">
+        <v>396.55768419999998</v>
+      </c>
+      <c r="O95">
+        <v>410.30153189999999</v>
+      </c>
+      <c r="P95">
+        <v>482.4</v>
+      </c>
+      <c r="Q95">
+        <v>441</v>
+      </c>
+      <c r="R95">
+        <v>404.1</v>
+      </c>
+      <c r="S95">
+        <v>383.4</v>
+      </c>
+      <c r="T95">
+        <v>358.2</v>
+      </c>
+      <c r="U95">
+        <v>204</v>
+      </c>
+      <c r="V95">
+        <v>229.89436799999999</v>
+      </c>
+      <c r="W95">
+        <v>333.86878899999999</v>
+      </c>
+      <c r="X95">
+        <v>344.14942230000003</v>
+      </c>
+      <c r="Y95">
+        <v>339</v>
+      </c>
+      <c r="Z95">
+        <v>266</v>
+      </c>
+      <c r="AA95">
+        <v>227</v>
+      </c>
+      <c r="AB95">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>41</v>
+      </c>
+      <c r="B96" t="s">
+        <v>46</v>
+      </c>
+      <c r="C96" t="s">
+        <v>51</v>
+      </c>
+      <c r="D96">
+        <v>384.67786769999998</v>
+      </c>
+      <c r="E96">
+        <v>16</v>
+      </c>
+      <c r="F96">
+        <v>15</v>
+      </c>
+      <c r="G96">
+        <v>35</v>
+      </c>
+      <c r="H96">
+        <v>30</v>
+      </c>
+      <c r="I96">
+        <v>22</v>
+      </c>
+      <c r="J96">
+        <v>14</v>
+      </c>
+      <c r="K96">
+        <v>6.3</v>
+      </c>
+      <c r="L96">
+        <v>6.0058660230000003</v>
+      </c>
+      <c r="M96">
+        <v>13.036161030000001</v>
+      </c>
+      <c r="N96">
+        <v>21.586809420000002</v>
+      </c>
+      <c r="O96">
+        <v>15.37619153</v>
+      </c>
+      <c r="P96">
+        <v>11.7</v>
+      </c>
+      <c r="Q96">
+        <v>15.3</v>
+      </c>
+      <c r="R96">
+        <v>15.3</v>
+      </c>
+      <c r="S96">
+        <v>14.4</v>
+      </c>
+      <c r="T96">
+        <v>8.1</v>
+      </c>
+      <c r="U96">
+        <v>9</v>
+      </c>
+      <c r="V96">
+        <v>1.206794583</v>
+      </c>
+      <c r="W96">
+        <v>13.35475156</v>
+      </c>
+      <c r="X96">
+        <v>26.011293550000001</v>
+      </c>
+      <c r="Y96">
+        <v>17</v>
+      </c>
+      <c r="Z96">
+        <v>27</v>
+      </c>
+      <c r="AA96">
+        <v>17</v>
+      </c>
+      <c r="AB96">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>41</v>
+      </c>
+      <c r="B97" t="s">
+        <v>52</v>
+      </c>
+      <c r="C97" t="s">
+        <v>47</v>
+      </c>
+      <c r="D97">
+        <v>63209.213329999999</v>
+      </c>
+      <c r="E97">
+        <v>456.18390799999997</v>
+      </c>
+      <c r="F97">
+        <v>342.89655169999997</v>
+      </c>
+      <c r="G97">
+        <v>378.29885059999998</v>
+      </c>
+      <c r="H97">
+        <v>684.78160920000005</v>
+      </c>
+      <c r="I97">
+        <v>1486.8965519999999</v>
+      </c>
+      <c r="J97">
+        <v>3747.8896549999999</v>
+      </c>
+      <c r="K97">
+        <v>5097.0206900000003</v>
+      </c>
+      <c r="L97">
+        <v>3185.4858559999998</v>
+      </c>
+      <c r="M97">
+        <v>2862.2201719999998</v>
+      </c>
+      <c r="N97">
+        <v>2950.1248620000001</v>
+      </c>
+      <c r="O97">
+        <v>2911.7133450000001</v>
+      </c>
+      <c r="P97">
+        <v>2934.0413789999998</v>
+      </c>
+      <c r="Q97">
+        <v>3239.9172410000001</v>
+      </c>
+      <c r="R97">
+        <v>3361.903448</v>
+      </c>
+      <c r="S97">
+        <v>3485.710345</v>
+      </c>
+      <c r="T97">
+        <v>3932.6896550000001</v>
+      </c>
+      <c r="U97">
+        <v>3639.2975540000002</v>
+      </c>
+      <c r="V97">
+        <v>3882.1659380000001</v>
+      </c>
+      <c r="W97">
+        <v>3945.5619259999999</v>
+      </c>
+      <c r="X97">
+        <v>3773.885057</v>
+      </c>
+      <c r="Y97">
+        <v>2540.8735630000001</v>
+      </c>
+      <c r="Z97">
+        <v>2262.7126440000002</v>
+      </c>
+      <c r="AA97">
+        <v>1254.252874</v>
+      </c>
+      <c r="AB97">
+        <v>852.68965519999995</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>41</v>
+      </c>
+      <c r="B98" t="s">
+        <v>52</v>
+      </c>
+      <c r="C98" t="s">
+        <v>48</v>
+      </c>
+      <c r="D98">
+        <v>1665.6016529999999</v>
+      </c>
+      <c r="E98">
+        <v>15.75</v>
+      </c>
+      <c r="F98">
+        <v>15.75</v>
+      </c>
+      <c r="G98">
+        <v>27</v>
+      </c>
+      <c r="H98">
+        <v>27</v>
+      </c>
+      <c r="I98">
+        <v>34.5</v>
+      </c>
+      <c r="J98">
+        <v>45.225000000000001</v>
+      </c>
+      <c r="K98">
+        <v>111.375</v>
+      </c>
+      <c r="L98">
+        <v>85.642889179999997</v>
+      </c>
+      <c r="M98">
+        <v>135.4281015</v>
+      </c>
+      <c r="N98">
+        <v>125.64333929999999</v>
+      </c>
+      <c r="O98">
+        <v>115.3954985</v>
+      </c>
+      <c r="P98">
+        <v>111.375</v>
+      </c>
+      <c r="Q98">
+        <v>95.174999999999997</v>
+      </c>
+      <c r="R98">
+        <v>124.2</v>
+      </c>
+      <c r="S98">
+        <v>104.625</v>
+      </c>
+      <c r="T98">
+        <v>106.65</v>
+      </c>
+      <c r="U98">
+        <v>89.86591215</v>
+      </c>
+      <c r="V98">
+        <v>78.125967750000001</v>
+      </c>
+      <c r="W98">
+        <v>84.274944379999994</v>
+      </c>
+      <c r="X98">
+        <v>33.6</v>
+      </c>
+      <c r="Y98">
+        <v>35.25</v>
+      </c>
+      <c r="Z98">
+        <v>18.75</v>
+      </c>
+      <c r="AA98">
+        <v>19.5</v>
+      </c>
+      <c r="AB98">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>41</v>
+      </c>
+      <c r="B99" t="s">
+        <v>52</v>
+      </c>
+      <c r="C99" t="s">
+        <v>49</v>
+      </c>
+      <c r="D99">
+        <v>625.98697460000005</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>18</v>
+      </c>
+      <c r="K99">
+        <v>45.9</v>
+      </c>
+      <c r="L99">
+        <v>33.695562959999997</v>
+      </c>
+      <c r="M99">
+        <v>55.675997279999997</v>
+      </c>
+      <c r="N99">
+        <v>49.419713450000003</v>
+      </c>
+      <c r="O99">
+        <v>60.828634899999997</v>
+      </c>
+      <c r="P99">
+        <v>54</v>
+      </c>
+      <c r="Q99">
+        <v>64.8</v>
+      </c>
+      <c r="R99">
+        <v>46.8</v>
+      </c>
+      <c r="S99">
+        <v>47.7</v>
+      </c>
+      <c r="T99">
+        <v>42.3</v>
+      </c>
+      <c r="U99">
+        <v>33.054128609999999</v>
+      </c>
+      <c r="V99">
+        <v>23.347990360000001</v>
+      </c>
+      <c r="W99">
+        <v>28.664947049999999</v>
+      </c>
+      <c r="X99">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="Y99">
+        <v>4</v>
+      </c>
+      <c r="Z99">
+        <v>7</v>
+      </c>
+      <c r="AA99">
+        <v>0</v>
+      </c>
+      <c r="AB99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>41</v>
+      </c>
+      <c r="B100" t="s">
+        <v>52</v>
+      </c>
+      <c r="C100" t="s">
+        <v>50</v>
+      </c>
+      <c r="D100">
+        <v>7225.3121300000003</v>
+      </c>
+      <c r="E100">
+        <v>204</v>
+      </c>
+      <c r="F100">
+        <v>184</v>
+      </c>
+      <c r="G100">
+        <v>193</v>
+      </c>
+      <c r="H100">
+        <v>242</v>
+      </c>
+      <c r="I100">
+        <v>227</v>
+      </c>
+      <c r="J100">
+        <v>278.10000000000002</v>
+      </c>
+      <c r="K100">
+        <v>324.89999999999998</v>
+      </c>
+      <c r="L100">
+        <v>229.62902170000001</v>
+      </c>
+      <c r="M100">
+        <v>322.7703085</v>
+      </c>
+      <c r="N100">
+        <v>411.27253059999998</v>
+      </c>
+      <c r="O100">
+        <v>407.90966930000002</v>
+      </c>
+      <c r="P100">
+        <v>403.2</v>
+      </c>
+      <c r="Q100">
+        <v>441</v>
+      </c>
+      <c r="R100">
+        <v>417.6</v>
+      </c>
+      <c r="S100">
+        <v>296.10000000000002</v>
+      </c>
+      <c r="T100">
+        <v>376.2</v>
+      </c>
+      <c r="U100">
+        <v>314.84057510000002</v>
+      </c>
+      <c r="V100">
+        <v>297.23787729999998</v>
+      </c>
+      <c r="W100">
+        <v>353.1521477</v>
+      </c>
+      <c r="X100">
+        <v>372.4</v>
+      </c>
+      <c r="Y100">
+        <v>251</v>
+      </c>
+      <c r="Z100">
+        <v>262</v>
+      </c>
+      <c r="AA100">
+        <v>203</v>
+      </c>
+      <c r="AB100">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>41</v>
+      </c>
+      <c r="B101" t="s">
+        <v>52</v>
+      </c>
+      <c r="C101" t="s">
+        <v>51</v>
+      </c>
+      <c r="D101">
+        <v>416.16642719999999</v>
+      </c>
+      <c r="E101">
+        <v>35</v>
+      </c>
+      <c r="F101">
+        <v>26</v>
+      </c>
+      <c r="G101">
+        <v>23</v>
+      </c>
+      <c r="H101">
+        <v>27</v>
+      </c>
+      <c r="I101">
+        <v>23</v>
+      </c>
+      <c r="J101">
+        <v>23.4</v>
+      </c>
+      <c r="K101">
+        <v>12.6</v>
+      </c>
+      <c r="L101">
+        <v>13.727821949999999</v>
+      </c>
+      <c r="M101">
+        <v>9.7809184410000007</v>
+      </c>
+      <c r="N101">
+        <v>17.5900675</v>
+      </c>
+      <c r="O101">
+        <v>12.52354248</v>
+      </c>
+      <c r="P101">
+        <v>16.2</v>
+      </c>
+      <c r="Q101">
+        <v>19.8</v>
+      </c>
+      <c r="R101">
+        <v>16.2</v>
+      </c>
+      <c r="S101">
+        <v>7.2</v>
+      </c>
+      <c r="T101">
+        <v>9</v>
+      </c>
+      <c r="U101">
+        <v>12.39529823</v>
+      </c>
+      <c r="V101">
+        <v>10.775995549999999</v>
+      </c>
+      <c r="W101">
+        <v>9.1727830570000002</v>
+      </c>
+      <c r="X101">
+        <v>2.8</v>
+      </c>
+      <c r="Y101">
+        <v>11</v>
+      </c>
+      <c r="Z101">
+        <v>29</v>
+      </c>
+      <c r="AA101">
+        <v>19</v>
+      </c>
+      <c r="AB101">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>40</v>
+      </c>
+      <c r="B102" t="s">
+        <v>46</v>
+      </c>
+      <c r="C102" t="s">
+        <v>47</v>
+      </c>
+      <c r="D102">
+        <v>45230.996890000002</v>
+      </c>
+      <c r="E102">
+        <v>371.21839080000001</v>
+      </c>
+      <c r="F102">
+        <v>235.67816089999999</v>
+      </c>
+      <c r="G102">
+        <v>186.11494250000001</v>
+      </c>
+      <c r="H102">
+        <v>272.09195399999999</v>
+      </c>
+      <c r="I102">
+        <v>566.43678160000002</v>
+      </c>
+      <c r="J102">
+        <v>1035.9724140000001</v>
+      </c>
+      <c r="K102">
+        <v>1794.289655</v>
+      </c>
+      <c r="L102">
+        <v>1617.9862069999999</v>
+      </c>
+      <c r="M102">
+        <v>1583.3931030000001</v>
+      </c>
+      <c r="N102">
+        <v>1454.1241379999999</v>
+      </c>
+      <c r="O102">
+        <v>1596.137931</v>
+      </c>
+      <c r="P102">
+        <v>2736.4965520000001</v>
+      </c>
+      <c r="Q102">
+        <v>3053.2965519999998</v>
+      </c>
+      <c r="R102">
+        <v>3206.2344830000002</v>
+      </c>
+      <c r="S102">
+        <v>3291.026801</v>
+      </c>
+      <c r="T102">
+        <v>2925.2413790000001</v>
+      </c>
+      <c r="U102">
+        <v>3412.7816090000001</v>
+      </c>
+      <c r="V102">
+        <v>3476.5057470000002</v>
+      </c>
+      <c r="W102">
+        <v>3993.3793099999998</v>
+      </c>
+      <c r="X102">
+        <v>3473.6735629999998</v>
+      </c>
+      <c r="Y102">
+        <v>1698.703448</v>
+      </c>
+      <c r="Z102">
+        <v>1396.4689659999999</v>
+      </c>
+      <c r="AA102">
+        <v>1107.2620429999999</v>
+      </c>
+      <c r="AB102">
+        <v>746.48275860000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>40</v>
+      </c>
+      <c r="B103" t="s">
+        <v>46</v>
+      </c>
+      <c r="C103" t="s">
+        <v>48</v>
+      </c>
+      <c r="D103">
+        <v>1172.7202560000001</v>
+      </c>
+      <c r="E103">
+        <v>6</v>
+      </c>
+      <c r="F103">
+        <v>2.25</v>
+      </c>
+      <c r="G103">
+        <v>3.75</v>
+      </c>
+      <c r="H103">
+        <v>12</v>
+      </c>
+      <c r="I103">
+        <v>35.25</v>
+      </c>
+      <c r="J103">
+        <v>49.274999999999999</v>
+      </c>
+      <c r="K103">
+        <v>64.125</v>
+      </c>
+      <c r="L103">
+        <v>61.2</v>
+      </c>
+      <c r="M103">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="N103">
+        <v>72</v>
+      </c>
+      <c r="O103">
+        <v>51.3</v>
+      </c>
+      <c r="P103">
+        <v>91.125</v>
+      </c>
+      <c r="Q103">
+        <v>116.77500000000001</v>
+      </c>
+      <c r="R103">
+        <v>111.375</v>
+      </c>
+      <c r="S103">
+        <v>83.743187699999993</v>
+      </c>
+      <c r="T103">
+        <v>65.25</v>
+      </c>
+      <c r="U103">
+        <v>58.8</v>
+      </c>
+      <c r="V103">
+        <v>63</v>
+      </c>
+      <c r="W103">
+        <v>79.8</v>
+      </c>
+      <c r="X103">
+        <v>44.1</v>
+      </c>
+      <c r="Y103">
+        <v>10.8</v>
+      </c>
+      <c r="Z103">
+        <v>12.15</v>
+      </c>
+      <c r="AA103">
+        <v>6.8020682710000004</v>
+      </c>
+      <c r="AB103">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>40</v>
+      </c>
+      <c r="B104" t="s">
+        <v>46</v>
+      </c>
+      <c r="C104" t="s">
+        <v>49</v>
+      </c>
+      <c r="D104">
+        <v>484.16202429999998</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+      <c r="F104">
+        <v>2</v>
+      </c>
+      <c r="G104">
+        <v>2</v>
+      </c>
+      <c r="H104">
+        <v>4</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="J104">
+        <v>15.3</v>
+      </c>
+      <c r="K104">
+        <v>40.5</v>
+      </c>
+      <c r="L104">
+        <v>32.4</v>
+      </c>
+      <c r="M104">
+        <v>31.2</v>
+      </c>
+      <c r="N104">
+        <v>36.6</v>
+      </c>
+      <c r="O104">
+        <v>30</v>
+      </c>
+      <c r="P104">
+        <v>52.2</v>
+      </c>
+      <c r="Q104">
+        <v>61.2</v>
+      </c>
+      <c r="R104">
+        <v>41.4</v>
+      </c>
+      <c r="S104">
+        <v>32.948139429999998</v>
+      </c>
+      <c r="T104">
+        <v>23</v>
+      </c>
+      <c r="U104">
+        <v>18.2</v>
+      </c>
+      <c r="V104">
+        <v>18.2</v>
+      </c>
+      <c r="W104">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="X104">
+        <v>11.2</v>
+      </c>
+      <c r="Y104">
+        <v>2.7</v>
+      </c>
+      <c r="Z104">
+        <v>2.7</v>
+      </c>
+      <c r="AA104">
+        <v>1.813884872</v>
+      </c>
+      <c r="AB104">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>40</v>
+      </c>
+      <c r="B105" t="s">
+        <v>46</v>
+      </c>
+      <c r="C105" t="s">
+        <v>50</v>
+      </c>
+      <c r="D105">
+        <v>3849.7341230000002</v>
+      </c>
+      <c r="E105">
+        <v>62</v>
+      </c>
+      <c r="F105">
+        <v>50</v>
+      </c>
+      <c r="G105">
+        <v>46</v>
+      </c>
+      <c r="H105">
+        <v>92</v>
+      </c>
+      <c r="I105">
+        <v>162</v>
+      </c>
+      <c r="J105">
+        <v>126.9</v>
+      </c>
+      <c r="K105">
+        <v>126</v>
+      </c>
+      <c r="L105">
+        <v>113.4</v>
+      </c>
+      <c r="M105">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="N105">
+        <v>165</v>
+      </c>
+      <c r="O105">
+        <v>184.2</v>
+      </c>
+      <c r="P105">
+        <v>289.8</v>
+      </c>
+      <c r="Q105">
+        <v>286.2</v>
+      </c>
+      <c r="R105">
+        <v>263.7</v>
+      </c>
+      <c r="S105">
+        <v>204.0954193</v>
+      </c>
+      <c r="T105">
+        <v>212</v>
+      </c>
+      <c r="U105">
+        <v>225.4</v>
+      </c>
+      <c r="V105">
+        <v>239.4</v>
+      </c>
+      <c r="W105">
+        <v>285.60000000000002</v>
+      </c>
+      <c r="X105">
+        <v>225.4</v>
+      </c>
+      <c r="Y105">
+        <v>104.4</v>
+      </c>
+      <c r="Z105">
+        <v>90</v>
+      </c>
+      <c r="AA105">
+        <v>83.438704119999997</v>
+      </c>
+      <c r="AB105">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>40</v>
+      </c>
+      <c r="B106" t="s">
+        <v>46</v>
+      </c>
+      <c r="C106" t="s">
+        <v>51</v>
+      </c>
+      <c r="D106">
+        <v>249.6677234</v>
+      </c>
+      <c r="E106">
+        <v>14</v>
+      </c>
+      <c r="F106">
+        <v>9</v>
+      </c>
+      <c r="G106">
+        <v>9</v>
+      </c>
+      <c r="H106">
+        <v>12</v>
+      </c>
+      <c r="I106">
+        <v>20</v>
+      </c>
+      <c r="J106">
+        <v>14.4</v>
+      </c>
+      <c r="K106">
+        <v>9</v>
+      </c>
+      <c r="L106">
+        <v>6.6</v>
+      </c>
+      <c r="M106">
+        <v>3</v>
+      </c>
+      <c r="N106">
+        <v>9.6</v>
+      </c>
+      <c r="O106">
+        <v>6.6</v>
+      </c>
+      <c r="P106">
+        <v>11.7</v>
+      </c>
+      <c r="Q106">
+        <v>8.1</v>
+      </c>
+      <c r="R106">
+        <v>9.9</v>
+      </c>
+      <c r="S106">
+        <v>5.4913565719999999</v>
+      </c>
+      <c r="T106">
+        <v>6</v>
+      </c>
+      <c r="U106">
+        <v>5.6</v>
+      </c>
+      <c r="V106">
+        <v>5.6</v>
+      </c>
+      <c r="W106">
+        <v>22.4</v>
+      </c>
+      <c r="X106">
+        <v>18.2</v>
+      </c>
+      <c r="Y106">
+        <v>14.4</v>
+      </c>
+      <c r="Z106">
+        <v>8.1</v>
+      </c>
+      <c r="AA106">
+        <v>9.9763667970000007</v>
+      </c>
+      <c r="AB106">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>40</v>
+      </c>
+      <c r="B107" t="s">
+        <v>52</v>
+      </c>
+      <c r="C107" t="s">
+        <v>47</v>
+      </c>
+      <c r="D107">
+        <v>46862.260690000003</v>
+      </c>
+      <c r="E107">
+        <v>331.77011490000001</v>
+      </c>
+      <c r="F107">
+        <v>172.96551719999999</v>
+      </c>
+      <c r="G107">
+        <v>151.72413789999999</v>
+      </c>
+      <c r="H107">
+        <v>226.5747126</v>
+      </c>
+      <c r="I107">
+        <v>554.29885060000004</v>
+      </c>
+      <c r="J107">
+        <v>1639.5310340000001</v>
+      </c>
+      <c r="K107">
+        <v>3131.5862069999998</v>
+      </c>
+      <c r="L107">
+        <v>3797.3732089999999</v>
+      </c>
+      <c r="M107">
+        <v>3963.0992849999998</v>
+      </c>
+      <c r="N107">
+        <v>3866.603521</v>
+      </c>
+      <c r="O107">
+        <v>2789.3121630000001</v>
+      </c>
+      <c r="P107">
+        <v>2826.6206900000002</v>
+      </c>
+      <c r="Q107">
+        <v>2772</v>
+      </c>
+      <c r="R107">
+        <v>2708.275862</v>
+      </c>
+      <c r="S107">
+        <v>2827.5310340000001</v>
+      </c>
+      <c r="T107">
+        <v>2876.6896550000001</v>
+      </c>
+      <c r="U107">
+        <v>2188.5933730000002</v>
+      </c>
+      <c r="V107">
+        <v>1924.4689659999999</v>
+      </c>
+      <c r="W107">
+        <v>2898.5291229999998</v>
+      </c>
+      <c r="X107">
+        <v>1167.0620690000001</v>
+      </c>
+      <c r="Y107">
+        <v>1332.7448280000001</v>
+      </c>
+      <c r="Z107">
+        <v>1160.6896549999999</v>
+      </c>
+      <c r="AA107">
+        <v>953.38909209999997</v>
+      </c>
+      <c r="AB107">
+        <v>600.82758620000004</v>
+      </c>
+    </row>
+    <row r="108" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>40</v>
+      </c>
+      <c r="B108" t="s">
+        <v>52</v>
+      </c>
+      <c r="C108" t="s">
+        <v>48</v>
+      </c>
+      <c r="D108">
+        <v>1183.6088299999999</v>
+      </c>
+      <c r="E108">
+        <v>9</v>
+      </c>
+      <c r="F108">
+        <v>7.5</v>
+      </c>
+      <c r="G108">
+        <v>5.25</v>
+      </c>
+      <c r="H108">
+        <v>5.25</v>
+      </c>
+      <c r="I108">
+        <v>11.25</v>
+      </c>
+      <c r="J108">
+        <v>19.574999999999999</v>
+      </c>
+      <c r="K108">
+        <v>47.924999999999997</v>
+      </c>
+      <c r="L108">
+        <v>88.135803379999999</v>
+      </c>
+      <c r="M108">
+        <v>109.4493066</v>
+      </c>
+      <c r="N108">
+        <v>136.56155219999999</v>
+      </c>
+      <c r="O108">
+        <v>100.0648521</v>
+      </c>
+      <c r="P108">
+        <v>110.7</v>
+      </c>
+      <c r="Q108">
+        <v>105.97499999999999</v>
+      </c>
+      <c r="R108">
+        <v>89.775000000000006</v>
+      </c>
+      <c r="S108">
+        <v>86.4</v>
+      </c>
+      <c r="T108">
+        <v>54.674999999999997</v>
+      </c>
+      <c r="U108">
+        <v>50.564120600000003</v>
+      </c>
+      <c r="V108">
+        <v>33.75</v>
+      </c>
+      <c r="W108">
+        <v>47.512394479999998</v>
+      </c>
+      <c r="X108">
+        <v>18.45</v>
+      </c>
+      <c r="Y108">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="Z108">
+        <v>11.475</v>
+      </c>
+      <c r="AA108">
+        <v>7.2208002440000003</v>
+      </c>
+      <c r="AB108">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="109" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>40</v>
+      </c>
+      <c r="B109" t="s">
+        <v>52</v>
+      </c>
+      <c r="C109" t="s">
+        <v>49</v>
+      </c>
+      <c r="D109">
+        <v>572.75399670000002</v>
+      </c>
+      <c r="E109">
+        <v>5</v>
+      </c>
+      <c r="F109">
+        <v>4</v>
+      </c>
+      <c r="G109">
+        <v>10</v>
+      </c>
+      <c r="H109">
+        <v>6</v>
+      </c>
+      <c r="I109">
+        <v>7</v>
+      </c>
+      <c r="J109">
+        <v>14.4</v>
+      </c>
+      <c r="K109">
+        <v>30.6</v>
+      </c>
+      <c r="L109">
+        <v>28.07866302</v>
+      </c>
+      <c r="M109">
+        <v>61.910718879999997</v>
+      </c>
+      <c r="N109">
+        <v>59.282534290000001</v>
+      </c>
+      <c r="O109">
+        <v>56.478321440000002</v>
+      </c>
+      <c r="P109">
+        <v>52.2</v>
+      </c>
+      <c r="Q109">
+        <v>53.1</v>
+      </c>
+      <c r="R109">
+        <v>43.2</v>
+      </c>
+      <c r="S109">
+        <v>42.3</v>
+      </c>
+      <c r="T109">
+        <v>28.8</v>
+      </c>
+      <c r="U109">
+        <v>16.152427410000001</v>
+      </c>
+      <c r="V109">
+        <v>10.8</v>
+      </c>
+      <c r="W109">
+        <v>15.83746483</v>
+      </c>
+      <c r="X109">
+        <v>6</v>
+      </c>
+      <c r="Y109">
+        <v>3.6</v>
+      </c>
+      <c r="Z109">
+        <v>7.2</v>
+      </c>
+      <c r="AA109">
+        <v>4.8138668290000002</v>
+      </c>
+      <c r="AB109">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>40</v>
+      </c>
+      <c r="B110" t="s">
+        <v>52</v>
+      </c>
+      <c r="C110" t="s">
+        <v>50</v>
+      </c>
+      <c r="D110">
+        <v>3584.7870160000002</v>
+      </c>
+      <c r="E110">
+        <v>94</v>
+      </c>
+      <c r="F110">
+        <v>81</v>
+      </c>
+      <c r="G110">
+        <v>65</v>
+      </c>
+      <c r="H110">
+        <v>75</v>
+      </c>
+      <c r="I110">
+        <v>93</v>
+      </c>
+      <c r="J110">
+        <v>78.3</v>
+      </c>
+      <c r="K110">
+        <v>97.2</v>
+      </c>
+      <c r="L110">
+        <v>151.83277039999999</v>
+      </c>
+      <c r="M110">
+        <v>270.85939509999997</v>
+      </c>
+      <c r="N110">
+        <v>335.58148870000002</v>
+      </c>
+      <c r="O110">
+        <v>252.9246569</v>
+      </c>
+      <c r="P110">
+        <v>251.1</v>
+      </c>
+      <c r="Q110">
+        <v>234</v>
+      </c>
+      <c r="R110">
+        <v>230.4</v>
+      </c>
+      <c r="S110">
+        <v>173.7</v>
+      </c>
+      <c r="T110">
+        <v>159.30000000000001</v>
+      </c>
+      <c r="U110">
+        <v>113.7692713</v>
+      </c>
+      <c r="V110">
+        <v>89.4</v>
+      </c>
+      <c r="W110">
+        <v>163.32385600000001</v>
+      </c>
+      <c r="X110">
+        <v>90.6</v>
+      </c>
+      <c r="Y110">
+        <v>128.69999999999999</v>
+      </c>
+      <c r="Z110">
+        <v>123.3</v>
+      </c>
+      <c r="AA110">
+        <v>116.49557729999999</v>
+      </c>
+      <c r="AB110">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="111" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>40</v>
+      </c>
+      <c r="B111" t="s">
+        <v>52</v>
+      </c>
+      <c r="C111" t="s">
+        <v>51</v>
+      </c>
+      <c r="D111">
+        <v>264.49309010000002</v>
+      </c>
+      <c r="E111">
+        <v>25</v>
+      </c>
+      <c r="F111">
+        <v>20</v>
+      </c>
+      <c r="G111">
+        <v>22</v>
+      </c>
+      <c r="H111">
+        <v>13</v>
+      </c>
+      <c r="I111">
+        <v>11</v>
+      </c>
+      <c r="J111">
+        <v>7.2</v>
+      </c>
+      <c r="K111">
+        <v>8.1</v>
+      </c>
+      <c r="L111">
+        <v>4.1598019290000003</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>13.76201689</v>
+      </c>
+      <c r="O111">
+        <v>11.45936957</v>
+      </c>
+      <c r="P111">
+        <v>8.1</v>
+      </c>
+      <c r="Q111">
+        <v>12.6</v>
+      </c>
+      <c r="R111">
+        <v>5.4</v>
+      </c>
+      <c r="S111">
+        <v>5.4</v>
+      </c>
+      <c r="T111">
+        <v>3.6</v>
+      </c>
+      <c r="U111">
+        <v>4.2136767160000002</v>
+      </c>
+      <c r="V111">
+        <v>2.4</v>
+      </c>
+      <c r="W111">
+        <v>6.9288908610000002</v>
+      </c>
+      <c r="X111">
+        <v>6.6</v>
+      </c>
+      <c r="Y111">
+        <v>11.7</v>
+      </c>
+      <c r="Z111">
+        <v>19.8</v>
+      </c>
+      <c r="AA111">
+        <v>24.06933415</v>
+      </c>
+      <c r="AB111">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>